--- a/docs/design-vi/ACSMS-SCR-023/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルアップロード画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-023/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルアップロード画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Đồng bộ với bản tiếng Nhật (bản này dừng ở 2026-05-27, trước bản JA v1.1 ngày 2026-07-02): ①bỏ 3 ca kiểm thử download theo quy cách v1.0 cũ (006・040・045 của bản cũ) — nội dung không còn đúng (giả định INSERT vào `t_file_download` với `download_type=2`, cài đặt hiện tại không làm vậy) và đã được TC-052/053 mới thay thế. ②đánh số lại 001〜049 để khớp 1:1 với bản tiếng Nhật (trước đó bị lệch 1〜3 số). Chưa ca nào được thực thi (toàn bộ ô kết quả là "-") nên việc đánh số lại không làm mất dữ liệu. ③tạo カテゴリ8 và bổ sung 5 ca (050〜054): liên kết với màn hình download SCR-022, link download trong email thông báo, preview, download đơn lẻ, và download hàng loạt ZIP</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6346,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ70"/>
+  <dimension ref="A1:BQ73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8174,7 +8234,7 @@
       <c r="BP17" s="10" t="n"/>
       <c r="BQ17" s="11" t="n"/>
     </row>
-    <row r="18" ht="256" customHeight="1">
+    <row r="18" ht="288" customHeight="1">
       <c r="A18" s="44" t="n">
         <v>6</v>
       </c>
@@ -8187,7 +8247,7 @@
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="46" t="inlineStr">
         <is>
-          <t>Vi phạm DataScope: JA_HONTEN download file của JA khác</t>
+          <t>Tấn công trực tiếp URL: JA_HONTEN chỉ định ID của JA khác để upload</t>
         </is>
       </c>
       <c r="F18" s="10" t="n"/>
@@ -8197,8 +8257,7 @@
       <c r="J18" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id = 12345）
-・Đã đăng nhập + đã xác thực MFA
-・Tồn tại file của JA khác（ja_id = 67890）（`file_upload_id = 202`）</t>
+・Đã đăng nhập + đã xác thực MFA</t>
         </is>
       </c>
       <c r="K18" s="10" t="n"/>
@@ -8223,7 +8282,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Gửi trực tiếp GET `/api/v1/file-upload/202/download` bằng DevTools (file ngoài scope JA của mình)
+            <t xml:space="preserve">Gửi trực tiếp POST `/api/v1/file-upload` bằng multipart/form-data qua DevTools. Chỉ định `ja_ids[]=67890`（ngoài scope JA của mình）+ 1 file hợp lệ
 </t>
           </r>
           <r>
@@ -8240,7 +8299,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận DB: `SELECT * FROM t_log WHERE result_status = 2 AND target_table = 't_file_upload' ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t>Xác nhận DB: `SELECT COUNT(*) FROM t_file_upload WHERE ja_id = 67890 AND deleted_at IS NULL`（so sánh số lượng trước và sau khi gửi）</t>
           </r>
         </is>
       </c>
@@ -8283,15 +8342,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Có từ 1 error log trở lên được record
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Binary của file không được trả về trong response
+            <t xml:space="preserve">・Record mới hướng tới JA khác（ja_id=67890）không được đăng ký vào `t_file_upload`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・File vật lý không được lưu vào storage
 </t>
           </r>
           <r>
@@ -8308,7 +8367,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Truy cập dữ liệu ngoài scope bị chặn bởi guard của BE API</t>
+            <t>・ja_ids trong request body được validate bằng DataScope phía server, và ID ngoài scope bị từ chối</t>
           </r>
         </is>
       </c>
@@ -8356,7 +8415,8 @@
       <c r="BJ18" s="11" t="n"/>
       <c r="BK18" s="46" t="inlineStr">
         <is>
-          <t>Critical — khi fail nghĩa là rò rỉ dữ liệu JA khác, xử lý như sự cố bảo mật.</t>
+          <t>Critical — khi fail nghĩa là ghi dữ liệu trái phép vào JA khác.
+---</t>
         </is>
       </c>
       <c r="BL18" s="10" t="n"/>
@@ -8366,191 +8426,74 @@
       <c r="BP18" s="10" t="n"/>
       <c r="BQ18" s="11" t="n"/>
     </row>
-    <row r="19" ht="288" customHeight="1">
-      <c r="A19" s="44" t="n">
-        <v>7</v>
-      </c>
-      <c r="B19" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-007</t>
-        </is>
-      </c>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>Hiển thị màn hình &amp; Responsive (Layout &amp; Responsive)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="46" t="inlineStr">
-        <is>
-          <t>Tấn công trực tiếp URL: JA_HONTEN chỉ định ID của JA khác để upload</t>
-        </is>
-      </c>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id = 12345）
-・Đã đăng nhập + đã xác thực MFA</t>
-        </is>
-      </c>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
       <c r="K19" s="10" t="n"/>
       <c r="L19" s="10" t="n"/>
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Gửi trực tiếp POST `/api/v1/file-upload` bằng multipart/form-data qua DevTools. Chỉ định `ja_ids[]=67890`（ngoài scope JA của mình）+ 1 file hợp lệ
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận DB: `SELECT COUNT(*) FROM t_file_upload WHERE ja_id = 67890 AND deleted_at IS NULL`（so sánh số lượng trước và sau khi gửi）</t>
-          </r>
-        </is>
-      </c>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
       <c r="R19" s="10" t="n"/>
       <c r="S19" s="10" t="n"/>
       <c r="T19" s="10" t="n"/>
       <c r="U19" s="10" t="n"/>
       <c r="V19" s="10" t="n"/>
-      <c r="W19" s="11" t="n"/>
-      <c r="X19" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Trả về HTTP 403 (`error_code: DATA_SCOPE_VIOLATION`, message `このデータへのアクセス権限がありません。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Record mới hướng tới JA khác（ja_id=67890）không được đăng ký vào `t_file_upload`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・File vật lý không được lưu vào storage
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・ja_ids trong request body được validate bằng DataScope phía server, và ID ngoài scope bị từ chối</t>
-          </r>
-        </is>
-      </c>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="n"/>
       <c r="Y19" s="10" t="n"/>
       <c r="Z19" s="10" t="n"/>
       <c r="AA19" s="10" t="n"/>
       <c r="AB19" s="10" t="n"/>
       <c r="AC19" s="10" t="n"/>
-      <c r="AD19" s="11" t="n"/>
-      <c r="AE19" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF19" s="11" t="n"/>
-      <c r="AG19" s="45" t="inlineStr"/>
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="10" t="n"/>
+      <c r="AG19" s="10" t="n"/>
       <c r="AH19" s="10" t="n"/>
-      <c r="AI19" s="11" t="n"/>
-      <c r="AJ19" s="45" t="inlineStr"/>
+      <c r="AI19" s="10" t="n"/>
+      <c r="AJ19" s="10" t="n"/>
       <c r="AK19" s="10" t="n"/>
-      <c r="AL19" s="11" t="n"/>
-      <c r="AM19" s="45" t="inlineStr"/>
+      <c r="AL19" s="10" t="n"/>
+      <c r="AM19" s="10" t="n"/>
       <c r="AN19" s="10" t="n"/>
-      <c r="AO19" s="11" t="n"/>
-      <c r="AP19" s="45" t="inlineStr"/>
+      <c r="AO19" s="10" t="n"/>
+      <c r="AP19" s="10" t="n"/>
       <c r="AQ19" s="10" t="n"/>
-      <c r="AR19" s="11" t="n"/>
-      <c r="AS19" s="45" t="inlineStr"/>
+      <c r="AR19" s="10" t="n"/>
+      <c r="AS19" s="10" t="n"/>
       <c r="AT19" s="10" t="n"/>
-      <c r="AU19" s="11" t="n"/>
-      <c r="AV19" s="45" t="inlineStr"/>
+      <c r="AU19" s="10" t="n"/>
+      <c r="AV19" s="10" t="n"/>
       <c r="AW19" s="10" t="n"/>
-      <c r="AX19" s="11" t="n"/>
-      <c r="AY19" s="45" t="inlineStr"/>
+      <c r="AX19" s="10" t="n"/>
+      <c r="AY19" s="10" t="n"/>
       <c r="AZ19" s="10" t="n"/>
-      <c r="BA19" s="11" t="n"/>
-      <c r="BB19" s="45" t="inlineStr"/>
+      <c r="BA19" s="10" t="n"/>
+      <c r="BB19" s="10" t="n"/>
       <c r="BC19" s="10" t="n"/>
-      <c r="BD19" s="11" t="n"/>
-      <c r="BE19" s="45" t="inlineStr"/>
+      <c r="BD19" s="10" t="n"/>
+      <c r="BE19" s="10" t="n"/>
       <c r="BF19" s="10" t="n"/>
-      <c r="BG19" s="11" t="n"/>
-      <c r="BH19" s="45" t="inlineStr"/>
+      <c r="BG19" s="10" t="n"/>
+      <c r="BH19" s="10" t="n"/>
       <c r="BI19" s="10" t="n"/>
-      <c r="BJ19" s="11" t="n"/>
-      <c r="BK19" s="46" t="inlineStr">
-        <is>
-          <t>Critical — khi fail nghĩa là ghi dữ liệu trái phép vào JA khác.
----</t>
-        </is>
-      </c>
+      <c r="BJ19" s="10" t="n"/>
+      <c r="BK19" s="10" t="n"/>
       <c r="BL19" s="10" t="n"/>
       <c r="BM19" s="10" t="n"/>
       <c r="BN19" s="10" t="n"/>
@@ -8558,74 +8501,143 @@
       <c r="BP19" s="10" t="n"/>
       <c r="BQ19" s="11" t="n"/>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>Hiển thị màn hình &amp; Responsive (Layout &amp; Responsive)</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n"/>
+    <row r="20" ht="112" customHeight="1">
+      <c r="A20" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-007</t>
+        </is>
+      </c>
       <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="46" t="inlineStr">
+        <is>
+          <t>Hiển thị màn hình ban đầu (toàn bộ mục trống)</t>
+        </is>
+      </c>
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="10" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA</t>
+        </is>
+      </c>
       <c r="K20" s="10" t="n"/>
       <c r="L20" s="10" t="n"/>
       <c r="M20" s="10" t="n"/>
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
-      <c r="P20" s="10" t="n"/>
-      <c r="Q20" s="10" t="n"/>
+      <c r="P20" s="11" t="n"/>
+      <c r="Q20" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Chuyển sang URL `/file-upload` và hiển thị màn hình</t>
+          </r>
+        </is>
+      </c>
       <c r="R20" s="10" t="n"/>
       <c r="S20" s="10" t="n"/>
       <c r="T20" s="10" t="n"/>
       <c r="U20" s="10" t="n"/>
       <c r="V20" s="10" t="n"/>
-      <c r="W20" s="10" t="n"/>
-      <c r="X20" s="10" t="n"/>
+      <c r="W20" s="11" t="n"/>
+      <c r="X20" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Màn hình được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Các mục nhập JA đối tượng, chọn file, ngày dự định xóa được hiển thị ở trạng thái ban đầu (trống/chưa chọn)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Không vỡ layout</t>
+          </r>
+        </is>
+      </c>
       <c r="Y20" s="10" t="n"/>
       <c r="Z20" s="10" t="n"/>
       <c r="AA20" s="10" t="n"/>
       <c r="AB20" s="10" t="n"/>
       <c r="AC20" s="10" t="n"/>
-      <c r="AD20" s="10" t="n"/>
-      <c r="AE20" s="10" t="n"/>
-      <c r="AF20" s="10" t="n"/>
-      <c r="AG20" s="10" t="n"/>
+      <c r="AD20" s="11" t="n"/>
+      <c r="AE20" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF20" s="11" t="n"/>
+      <c r="AG20" s="45" t="inlineStr"/>
       <c r="AH20" s="10" t="n"/>
-      <c r="AI20" s="10" t="n"/>
-      <c r="AJ20" s="10" t="n"/>
+      <c r="AI20" s="11" t="n"/>
+      <c r="AJ20" s="45" t="inlineStr"/>
       <c r="AK20" s="10" t="n"/>
-      <c r="AL20" s="10" t="n"/>
-      <c r="AM20" s="10" t="n"/>
+      <c r="AL20" s="11" t="n"/>
+      <c r="AM20" s="45" t="inlineStr"/>
       <c r="AN20" s="10" t="n"/>
-      <c r="AO20" s="10" t="n"/>
-      <c r="AP20" s="10" t="n"/>
+      <c r="AO20" s="11" t="n"/>
+      <c r="AP20" s="45" t="inlineStr"/>
       <c r="AQ20" s="10" t="n"/>
-      <c r="AR20" s="10" t="n"/>
-      <c r="AS20" s="10" t="n"/>
+      <c r="AR20" s="11" t="n"/>
+      <c r="AS20" s="45" t="inlineStr"/>
       <c r="AT20" s="10" t="n"/>
-      <c r="AU20" s="10" t="n"/>
-      <c r="AV20" s="10" t="n"/>
+      <c r="AU20" s="11" t="n"/>
+      <c r="AV20" s="45" t="inlineStr"/>
       <c r="AW20" s="10" t="n"/>
-      <c r="AX20" s="10" t="n"/>
-      <c r="AY20" s="10" t="n"/>
+      <c r="AX20" s="11" t="n"/>
+      <c r="AY20" s="45" t="inlineStr"/>
       <c r="AZ20" s="10" t="n"/>
-      <c r="BA20" s="10" t="n"/>
-      <c r="BB20" s="10" t="n"/>
+      <c r="BA20" s="11" t="n"/>
+      <c r="BB20" s="45" t="inlineStr"/>
       <c r="BC20" s="10" t="n"/>
-      <c r="BD20" s="10" t="n"/>
-      <c r="BE20" s="10" t="n"/>
+      <c r="BD20" s="11" t="n"/>
+      <c r="BE20" s="45" t="inlineStr"/>
       <c r="BF20" s="10" t="n"/>
-      <c r="BG20" s="10" t="n"/>
-      <c r="BH20" s="10" t="n"/>
+      <c r="BG20" s="11" t="n"/>
+      <c r="BH20" s="45" t="inlineStr"/>
       <c r="BI20" s="10" t="n"/>
-      <c r="BJ20" s="10" t="n"/>
-      <c r="BK20" s="10" t="n"/>
+      <c r="BJ20" s="11" t="n"/>
+      <c r="BK20" s="46" t="inlineStr"/>
       <c r="BL20" s="10" t="n"/>
       <c r="BM20" s="10" t="n"/>
       <c r="BN20" s="10" t="n"/>
@@ -8633,7 +8645,7 @@
       <c r="BP20" s="10" t="n"/>
       <c r="BQ20" s="11" t="n"/>
     </row>
-    <row r="21" ht="112" customHeight="1">
+    <row r="21" ht="224" customHeight="1">
       <c r="A21" s="44" t="n">
         <v>8</v>
       </c>
@@ -8646,7 +8658,7 @@
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị màn hình ban đầu (toàn bộ mục trống)</t>
+          <t>Hiển thị khu vực chọn JA đối tượng</t>
         </is>
       </c>
       <c r="F21" s="10" t="n"/>
@@ -8681,7 +8693,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chuyển sang URL `/file-upload` và hiển thị màn hình</t>
+            <t xml:space="preserve">Xác nhận khu vực「対象JA選択」trên màn hình
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Click select box「都道府県コード」, tiếp theo xác nhận select box「対象JA」</t>
           </r>
         </is>
       </c>
@@ -8707,23 +8736,40 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Màn hình được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Các mục nhập JA đối tượng, chọn file, ngày dự định xóa được hiển thị ở trạng thái ban đầu (trống/chưa chọn)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Không vỡ layout</t>
+            <t xml:space="preserve">・Các select box「都道府県コード」「都道府県名」「対象JA」, button「追加」, button「削除」được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「都道府県名」được hiển thị ở dạng read-only
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Danh sách JA code + JA name được hiển thị trong select box「対象JA」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Có thể tìm kiếm trong select box「対象JA」</t>
           </r>
         </is>
       </c>
@@ -8777,7 +8823,7 @@
       <c r="BP21" s="10" t="n"/>
       <c r="BQ21" s="11" t="n"/>
     </row>
-    <row r="22" ht="224" customHeight="1">
+    <row r="22" ht="192" customHeight="1">
       <c r="A22" s="44" t="n">
         <v>9</v>
       </c>
@@ -8790,7 +8836,7 @@
       <c r="D22" s="11" t="n"/>
       <c r="E22" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị khu vực chọn JA đối tượng</t>
+          <t>Hiển thị khu vực chọn file</t>
         </is>
       </c>
       <c r="F22" s="10" t="n"/>
@@ -8825,7 +8871,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận khu vực「対象JA選択」trên màn hình
+            <t xml:space="preserve">Xác nhận khu vực「ファイル選択」trên màn hình
 </t>
           </r>
           <r>
@@ -8842,7 +8888,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Click select box「都道府県コード」, tiếp theo xác nhận select box「対象JA」</t>
+            <t>Sau khi chọn 1 file, xác nhận mục「削除予定日」</t>
           </r>
         </is>
       </c>
@@ -8868,15 +8914,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Các select box「都道府県コード」「都道府県名」「対象JA」, button「追加」, button「削除」được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・「都道府県名」được hiển thị ở dạng read-only
+            <t xml:space="preserve">・Khu vực chọn file hỗ trợ drag and drop và button「参照」được hiển thị
 </t>
           </r>
           <r>
@@ -8893,15 +8931,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Danh sách JA code + JA name được hiển thị trong select box「対象JA」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Có thể tìm kiếm trong select box「対象JA」</t>
+            <t xml:space="preserve">・「削除予定日」được hiển thị dưới dạng mục nhập calendar
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・File đã chọn được hiển thị trong danh sách theo định dạng「tên file + size」</t>
           </r>
         </is>
       </c>
@@ -8955,7 +8993,7 @@
       <c r="BP22" s="10" t="n"/>
       <c r="BQ22" s="11" t="n"/>
     </row>
-    <row r="23" ht="192" customHeight="1">
+    <row r="23" ht="64" customHeight="1">
       <c r="A23" s="44" t="n">
         <v>10</v>
       </c>
@@ -8968,7 +9006,7 @@
       <c r="D23" s="11" t="n"/>
       <c r="E23" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị khu vực chọn file</t>
+          <t>Hiển thị action button</t>
         </is>
       </c>
       <c r="F23" s="10" t="n"/>
@@ -9003,24 +9041,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận khu vực「ファイル選択」trên màn hình
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Sau khi chọn 1 file, xác nhận mục「削除予定日」</t>
+            <t>Xác nhận khu vực action button ở phía dưới màn hình</t>
           </r>
         </is>
       </c>
@@ -9046,32 +9067,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Khu vực chọn file hỗ trợ drag and drop và button「参照」được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・「削除予定日」được hiển thị dưới dạng mục nhập calendar
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・File đã chọn được hiển thị trong danh sách theo định dạng「tên file + size」</t>
+            <t>・Button「アップロード実行」và button「クリア」được hiển thị</t>
           </r>
         </is>
       </c>
@@ -9125,7 +9121,7 @@
       <c r="BP23" s="10" t="n"/>
       <c r="BQ23" s="11" t="n"/>
     </row>
-    <row r="24" ht="64" customHeight="1">
+    <row r="24" ht="336" customHeight="1">
       <c r="A24" s="44" t="n">
         <v>11</v>
       </c>
@@ -9138,7 +9134,7 @@
       <c r="D24" s="11" t="n"/>
       <c r="E24" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị action button</t>
+          <t>Hiển thị bảng danh sách file đã upload</t>
         </is>
       </c>
       <c r="F24" s="10" t="n"/>
@@ -9148,7 +9144,8 @@
       <c r="J24" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
+・Đã đăng nhập + đã xác thực MFA
+・Tồn tại nhiều file đã upload (mỗi loại từ 1 row trở lên: row có `deleted_at` NULL và row có `deleted_at` NOT NULL)</t>
         </is>
       </c>
       <c r="K24" s="10" t="n"/>
@@ -9173,7 +9170,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận khu vực action button ở phía dưới màn hình</t>
+            <t xml:space="preserve">Xác nhận bảng「アップロードされたファイルリスト」ở phía dưới màn hình
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận trạng thái của cột「通知ステータス」và button「削除」của từng row</t>
           </r>
         </is>
       </c>
@@ -9199,7 +9213,48 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Button「アップロード実行」và button「クリア」được hiển thị</t>
+            <t xml:space="preserve">・Các cột「ファイル名」「サイズ」「通知ステータス」「削除予定日」「削除日」「操作（削除ボタン）」được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Cột「削除日」hiển thị「-」khi `deleted_at` là NULL, hiển thị theo định dạng yyyymmdd khi NOT NULL
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Một trong các badge「未送信」「送信中」「完了」「一部失敗」được hiển thị ở cột「通知ステータス」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Row có `deleted_at` NULL thì button「削除」được hiển thị ở trạng thái active
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Row có `deleted_at` NOT NULL thì button「削除」được hiển thị ở trạng thái disable</t>
           </r>
         </is>
       </c>
@@ -9253,7 +9308,7 @@
       <c r="BP24" s="10" t="n"/>
       <c r="BQ24" s="11" t="n"/>
     </row>
-    <row r="25" ht="336" customHeight="1">
+    <row r="25" ht="80" customHeight="1">
       <c r="A25" s="44" t="n">
         <v>12</v>
       </c>
@@ -9266,7 +9321,7 @@
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị bảng danh sách file đã upload</t>
+          <t>Hiển thị responsive (không vỡ layout)</t>
         </is>
       </c>
       <c r="F25" s="10" t="n"/>
@@ -9276,8 +9331,7 @@
       <c r="J25" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA
-・Tồn tại nhiều file đã upload (mỗi loại từ 1 row trở lên: row có `deleted_at` NULL và row có `deleted_at` NOT NULL)</t>
+・Đã đăng nhập + đã xác thực MFA</t>
         </is>
       </c>
       <c r="K25" s="10" t="n"/>
@@ -9302,24 +9356,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận bảng「アップロードされたファイルリスト」ở phía dưới màn hình
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận trạng thái của cột「通知ステータス」và button「削除」của từng row</t>
+            <t>Thay đổi chiều rộng browser sang các breakpoint 1280px / 768px / 375px và xác nhận màn hình</t>
           </r>
         </is>
       </c>
@@ -9345,48 +9382,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Các cột「ファイル名」「サイズ」「通知ステータス」「削除予定日」「削除日」「操作（削除ボタン）」được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Cột「削除日」hiển thị「-」khi `deleted_at` là NULL, hiển thị theo định dạng yyyymmdd khi NOT NULL
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Một trong các badge「未送信」「送信中」「完了」「一部失敗」được hiển thị ở cột「通知ステータス」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Row có `deleted_at` NULL thì button「削除」được hiển thị ở trạng thái active
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Row có `deleted_at` NOT NULL thì button「削除」được hiển thị ở trạng thái disable</t>
+            <t xml:space="preserve">・Không vỡ layout ở mỗi breakpoint
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Không phát sinh scroll ngang ngoài ý muốn</t>
           </r>
         </is>
       </c>
@@ -9440,7 +9444,7 @@
       <c r="BP25" s="10" t="n"/>
       <c r="BQ25" s="11" t="n"/>
     </row>
-    <row r="26" ht="80" customHeight="1">
+    <row r="26" ht="160" customHeight="1">
       <c r="A26" s="44" t="n">
         <v>13</v>
       </c>
@@ -9453,7 +9457,7 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị responsive (không vỡ layout)</t>
+          <t>Thao tác bàn phím (thứ tự Tab)</t>
         </is>
       </c>
       <c r="F26" s="10" t="n"/>
@@ -9488,7 +9492,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Thay đổi chiều rộng browser sang các breakpoint 1280px / 768px / 375px và xác nhận màn hình</t>
+            <t xml:space="preserve">Di chuyển lần lượt qua từng mục nhập・button bằng phím Tab
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Focus vào button bằng phím Enter và xác nhận thao tác</t>
           </r>
         </is>
       </c>
@@ -9514,15 +9535,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Không vỡ layout ở mỗi breakpoint
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Không phát sinh scroll ngang ngoài ý muốn</t>
+            <t xml:space="preserve">・Thứ tự Tab tuân theo thứ tự hiển thị của màn hình (JA đối tượng → chọn file → ngày dự định xóa → action button)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Button được focus có thể thao tác bằng phím Enter</t>
           </r>
         </is>
       </c>
@@ -9568,7 +9598,12 @@
       <c r="BH26" s="45" t="inlineStr"/>
       <c r="BI26" s="10" t="n"/>
       <c r="BJ26" s="11" t="n"/>
-      <c r="BK26" s="46" t="inlineStr"/>
+      <c r="BK26" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL26" s="10" t="n"/>
       <c r="BM26" s="10" t="n"/>
       <c r="BN26" s="10" t="n"/>
@@ -9576,166 +9611,74 @@
       <c r="BP26" s="10" t="n"/>
       <c r="BQ26" s="11" t="n"/>
     </row>
-    <row r="27" ht="160" customHeight="1">
-      <c r="A27" s="44" t="n">
-        <v>14</v>
-      </c>
-      <c r="B27" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-014</t>
-        </is>
-      </c>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>Header &amp; Breadcrumb (Header &amp; Breadcrumb)</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="46" t="inlineStr">
-        <is>
-          <t>Thao tác bàn phím (thứ tự Tab)</t>
-        </is>
-      </c>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
-        </is>
-      </c>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="10" t="n"/>
       <c r="M27" s="10" t="n"/>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Di chuyển lần lượt qua từng mục nhập・button bằng phím Tab
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Focus vào button bằng phím Enter và xác nhận thao tác</t>
-          </r>
-        </is>
-      </c>
+      <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="10" t="n"/>
       <c r="R27" s="10" t="n"/>
       <c r="S27" s="10" t="n"/>
       <c r="T27" s="10" t="n"/>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
-      <c r="W27" s="11" t="n"/>
-      <c r="X27" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Thứ tự Tab tuân theo thứ tự hiển thị của màn hình (JA đối tượng → chọn file → ngày dự định xóa → action button)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Button được focus có thể thao tác bằng phím Enter</t>
-          </r>
-        </is>
-      </c>
+      <c r="W27" s="10" t="n"/>
+      <c r="X27" s="10" t="n"/>
       <c r="Y27" s="10" t="n"/>
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
       <c r="AB27" s="10" t="n"/>
       <c r="AC27" s="10" t="n"/>
-      <c r="AD27" s="11" t="n"/>
-      <c r="AE27" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF27" s="11" t="n"/>
-      <c r="AG27" s="45" t="inlineStr"/>
+      <c r="AD27" s="10" t="n"/>
+      <c r="AE27" s="10" t="n"/>
+      <c r="AF27" s="10" t="n"/>
+      <c r="AG27" s="10" t="n"/>
       <c r="AH27" s="10" t="n"/>
-      <c r="AI27" s="11" t="n"/>
-      <c r="AJ27" s="45" t="inlineStr"/>
+      <c r="AI27" s="10" t="n"/>
+      <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="10" t="n"/>
-      <c r="AL27" s="11" t="n"/>
-      <c r="AM27" s="45" t="inlineStr"/>
+      <c r="AL27" s="10" t="n"/>
+      <c r="AM27" s="10" t="n"/>
       <c r="AN27" s="10" t="n"/>
-      <c r="AO27" s="11" t="n"/>
-      <c r="AP27" s="45" t="inlineStr"/>
+      <c r="AO27" s="10" t="n"/>
+      <c r="AP27" s="10" t="n"/>
       <c r="AQ27" s="10" t="n"/>
-      <c r="AR27" s="11" t="n"/>
-      <c r="AS27" s="45" t="inlineStr"/>
+      <c r="AR27" s="10" t="n"/>
+      <c r="AS27" s="10" t="n"/>
       <c r="AT27" s="10" t="n"/>
-      <c r="AU27" s="11" t="n"/>
-      <c r="AV27" s="45" t="inlineStr"/>
+      <c r="AU27" s="10" t="n"/>
+      <c r="AV27" s="10" t="n"/>
       <c r="AW27" s="10" t="n"/>
-      <c r="AX27" s="11" t="n"/>
-      <c r="AY27" s="45" t="inlineStr"/>
+      <c r="AX27" s="10" t="n"/>
+      <c r="AY27" s="10" t="n"/>
       <c r="AZ27" s="10" t="n"/>
-      <c r="BA27" s="11" t="n"/>
-      <c r="BB27" s="45" t="inlineStr"/>
+      <c r="BA27" s="10" t="n"/>
+      <c r="BB27" s="10" t="n"/>
       <c r="BC27" s="10" t="n"/>
-      <c r="BD27" s="11" t="n"/>
-      <c r="BE27" s="45" t="inlineStr"/>
+      <c r="BD27" s="10" t="n"/>
+      <c r="BE27" s="10" t="n"/>
       <c r="BF27" s="10" t="n"/>
-      <c r="BG27" s="11" t="n"/>
-      <c r="BH27" s="45" t="inlineStr"/>
+      <c r="BG27" s="10" t="n"/>
+      <c r="BH27" s="10" t="n"/>
       <c r="BI27" s="10" t="n"/>
-      <c r="BJ27" s="11" t="n"/>
-      <c r="BK27" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BJ27" s="10" t="n"/>
+      <c r="BK27" s="10" t="n"/>
       <c r="BL27" s="10" t="n"/>
       <c r="BM27" s="10" t="n"/>
       <c r="BN27" s="10" t="n"/>
@@ -9743,74 +9686,127 @@
       <c r="BP27" s="10" t="n"/>
       <c r="BQ27" s="11" t="n"/>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>Header &amp; Breadcrumb (Header &amp; Breadcrumb)</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n"/>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="44" t="n">
+        <v>14</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-014</t>
+        </is>
+      </c>
       <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="46" t="inlineStr">
+        <is>
+          <t>Hiển thị breadcrumb</t>
+        </is>
+      </c>
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA</t>
+        </is>
+      </c>
       <c r="K28" s="10" t="n"/>
       <c r="L28" s="10" t="n"/>
       <c r="M28" s="10" t="n"/>
       <c r="N28" s="10" t="n"/>
       <c r="O28" s="10" t="n"/>
-      <c r="P28" s="10" t="n"/>
-      <c r="Q28" s="10" t="n"/>
+      <c r="P28" s="11" t="n"/>
+      <c r="Q28" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Chuyển sang URL `/file-upload` và xác nhận breadcrumb ở phía trên màn hình</t>
+          </r>
+        </is>
+      </c>
       <c r="R28" s="10" t="n"/>
       <c r="S28" s="10" t="n"/>
       <c r="T28" s="10" t="n"/>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
-      <c r="W28" s="10" t="n"/>
-      <c r="X28" s="10" t="n"/>
+      <c r="W28" s="11" t="n"/>
+      <c r="X28" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Breadcrumb hiển thị「ホーム ＞ ファイルアップロード」</t>
+          </r>
+        </is>
+      </c>
       <c r="Y28" s="10" t="n"/>
       <c r="Z28" s="10" t="n"/>
       <c r="AA28" s="10" t="n"/>
       <c r="AB28" s="10" t="n"/>
       <c r="AC28" s="10" t="n"/>
-      <c r="AD28" s="10" t="n"/>
-      <c r="AE28" s="10" t="n"/>
-      <c r="AF28" s="10" t="n"/>
-      <c r="AG28" s="10" t="n"/>
+      <c r="AD28" s="11" t="n"/>
+      <c r="AE28" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF28" s="11" t="n"/>
+      <c r="AG28" s="45" t="inlineStr"/>
       <c r="AH28" s="10" t="n"/>
-      <c r="AI28" s="10" t="n"/>
-      <c r="AJ28" s="10" t="n"/>
+      <c r="AI28" s="11" t="n"/>
+      <c r="AJ28" s="45" t="inlineStr"/>
       <c r="AK28" s="10" t="n"/>
-      <c r="AL28" s="10" t="n"/>
-      <c r="AM28" s="10" t="n"/>
+      <c r="AL28" s="11" t="n"/>
+      <c r="AM28" s="45" t="inlineStr"/>
       <c r="AN28" s="10" t="n"/>
-      <c r="AO28" s="10" t="n"/>
-      <c r="AP28" s="10" t="n"/>
+      <c r="AO28" s="11" t="n"/>
+      <c r="AP28" s="45" t="inlineStr"/>
       <c r="AQ28" s="10" t="n"/>
-      <c r="AR28" s="10" t="n"/>
-      <c r="AS28" s="10" t="n"/>
+      <c r="AR28" s="11" t="n"/>
+      <c r="AS28" s="45" t="inlineStr"/>
       <c r="AT28" s="10" t="n"/>
-      <c r="AU28" s="10" t="n"/>
-      <c r="AV28" s="10" t="n"/>
+      <c r="AU28" s="11" t="n"/>
+      <c r="AV28" s="45" t="inlineStr"/>
       <c r="AW28" s="10" t="n"/>
-      <c r="AX28" s="10" t="n"/>
-      <c r="AY28" s="10" t="n"/>
+      <c r="AX28" s="11" t="n"/>
+      <c r="AY28" s="45" t="inlineStr"/>
       <c r="AZ28" s="10" t="n"/>
-      <c r="BA28" s="10" t="n"/>
-      <c r="BB28" s="10" t="n"/>
+      <c r="BA28" s="11" t="n"/>
+      <c r="BB28" s="45" t="inlineStr"/>
       <c r="BC28" s="10" t="n"/>
-      <c r="BD28" s="10" t="n"/>
-      <c r="BE28" s="10" t="n"/>
+      <c r="BD28" s="11" t="n"/>
+      <c r="BE28" s="45" t="inlineStr"/>
       <c r="BF28" s="10" t="n"/>
-      <c r="BG28" s="10" t="n"/>
-      <c r="BH28" s="10" t="n"/>
+      <c r="BG28" s="11" t="n"/>
+      <c r="BH28" s="45" t="inlineStr"/>
       <c r="BI28" s="10" t="n"/>
-      <c r="BJ28" s="10" t="n"/>
-      <c r="BK28" s="10" t="n"/>
+      <c r="BJ28" s="11" t="n"/>
+      <c r="BK28" s="46" t="inlineStr"/>
       <c r="BL28" s="10" t="n"/>
       <c r="BM28" s="10" t="n"/>
       <c r="BN28" s="10" t="n"/>
@@ -9818,7 +9814,7 @@
       <c r="BP28" s="10" t="n"/>
       <c r="BQ28" s="11" t="n"/>
     </row>
-    <row r="29" ht="64" customHeight="1">
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="44" t="n">
         <v>15</v>
       </c>
@@ -9831,7 +9827,7 @@
       <c r="D29" s="11" t="n"/>
       <c r="E29" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị breadcrumb</t>
+          <t>Click「ホーム」trên breadcrumb để chuyển về dashboard</t>
         </is>
       </c>
       <c r="F29" s="10" t="n"/>
@@ -9866,7 +9862,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chuyển sang URL `/file-upload` và xác nhận breadcrumb ở phía trên màn hình</t>
+            <t>Click「ホーム」trên breadcrumb</t>
           </r>
         </is>
       </c>
@@ -9892,7 +9888,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Breadcrumb hiển thị「ホーム ＞ ファイルアップロード」</t>
+            <t>・Chuyển sang `/dashboard`</t>
           </r>
         </is>
       </c>
@@ -9959,7 +9955,7 @@
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="46" t="inlineStr">
         <is>
-          <t>Click「ホーム」trên breadcrumb để chuyển về dashboard</t>
+          <t>Hiển thị tiêu đề trang</t>
         </is>
       </c>
       <c r="F30" s="10" t="n"/>
@@ -9994,7 +9990,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Click「ホーム」trên breadcrumb</t>
+            <t>Chuyển sang URL `/file-upload` và xác nhận tiêu đề trang</t>
           </r>
         </is>
       </c>
@@ -10020,7 +10016,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Chuyển sang `/dashboard`</t>
+            <t>・Tiêu đề trang hiển thị「ファイルアップロード画面」</t>
           </r>
         </is>
       </c>
@@ -10087,7 +10083,7 @@
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị tiêu đề trang</t>
+          <t>Tên người dùng đăng nhập được hiển thị trên header</t>
         </is>
       </c>
       <c r="F31" s="10" t="n"/>
@@ -10122,7 +10118,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chuyển sang URL `/file-upload` và xác nhận tiêu đề trang</t>
+            <t>Xác nhận header ở phía trên màn hình</t>
           </r>
         </is>
       </c>
@@ -10148,7 +10144,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Tiêu đề trang hiển thị「ファイルアップロード画面」</t>
+            <t>・Tên người dùng đăng nhập được hiển thị</t>
           </r>
         </is>
       </c>
@@ -10194,7 +10190,12 @@
       <c r="BH31" s="45" t="inlineStr"/>
       <c r="BI31" s="10" t="n"/>
       <c r="BJ31" s="11" t="n"/>
-      <c r="BK31" s="46" t="inlineStr"/>
+      <c r="BK31" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL31" s="10" t="n"/>
       <c r="BM31" s="10" t="n"/>
       <c r="BN31" s="10" t="n"/>
@@ -10202,132 +10203,74 @@
       <c r="BP31" s="10" t="n"/>
       <c r="BQ31" s="11" t="n"/>
     </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="44" t="n">
-        <v>18</v>
-      </c>
-      <c r="B32" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-018</t>
-        </is>
-      </c>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>Kiểm tra dữ liệu nhập (Input Validation)</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="46" t="inlineStr">
-        <is>
-          <t>Tên người dùng đăng nhập được hiển thị trên header</t>
-        </is>
-      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
-        </is>
-      </c>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="10" t="n"/>
       <c r="M32" s="10" t="n"/>
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận header ở phía trên màn hình</t>
-          </r>
-        </is>
-      </c>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
       <c r="R32" s="10" t="n"/>
       <c r="S32" s="10" t="n"/>
       <c r="T32" s="10" t="n"/>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
-      <c r="W32" s="11" t="n"/>
-      <c r="X32" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Tên người dùng đăng nhập được hiển thị</t>
-          </r>
-        </is>
-      </c>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="n"/>
       <c r="Y32" s="10" t="n"/>
       <c r="Z32" s="10" t="n"/>
       <c r="AA32" s="10" t="n"/>
       <c r="AB32" s="10" t="n"/>
       <c r="AC32" s="10" t="n"/>
-      <c r="AD32" s="11" t="n"/>
-      <c r="AE32" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF32" s="11" t="n"/>
-      <c r="AG32" s="45" t="inlineStr"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="10" t="n"/>
+      <c r="AF32" s="10" t="n"/>
+      <c r="AG32" s="10" t="n"/>
       <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="11" t="n"/>
-      <c r="AJ32" s="45" t="inlineStr"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="10" t="n"/>
-      <c r="AL32" s="11" t="n"/>
-      <c r="AM32" s="45" t="inlineStr"/>
+      <c r="AL32" s="10" t="n"/>
+      <c r="AM32" s="10" t="n"/>
       <c r="AN32" s="10" t="n"/>
-      <c r="AO32" s="11" t="n"/>
-      <c r="AP32" s="45" t="inlineStr"/>
+      <c r="AO32" s="10" t="n"/>
+      <c r="AP32" s="10" t="n"/>
       <c r="AQ32" s="10" t="n"/>
-      <c r="AR32" s="11" t="n"/>
-      <c r="AS32" s="45" t="inlineStr"/>
+      <c r="AR32" s="10" t="n"/>
+      <c r="AS32" s="10" t="n"/>
       <c r="AT32" s="10" t="n"/>
-      <c r="AU32" s="11" t="n"/>
-      <c r="AV32" s="45" t="inlineStr"/>
+      <c r="AU32" s="10" t="n"/>
+      <c r="AV32" s="10" t="n"/>
       <c r="AW32" s="10" t="n"/>
-      <c r="AX32" s="11" t="n"/>
-      <c r="AY32" s="45" t="inlineStr"/>
+      <c r="AX32" s="10" t="n"/>
+      <c r="AY32" s="10" t="n"/>
       <c r="AZ32" s="10" t="n"/>
-      <c r="BA32" s="11" t="n"/>
-      <c r="BB32" s="45" t="inlineStr"/>
+      <c r="BA32" s="10" t="n"/>
+      <c r="BB32" s="10" t="n"/>
       <c r="BC32" s="10" t="n"/>
-      <c r="BD32" s="11" t="n"/>
-      <c r="BE32" s="45" t="inlineStr"/>
+      <c r="BD32" s="10" t="n"/>
+      <c r="BE32" s="10" t="n"/>
       <c r="BF32" s="10" t="n"/>
-      <c r="BG32" s="11" t="n"/>
-      <c r="BH32" s="45" t="inlineStr"/>
+      <c r="BG32" s="10" t="n"/>
+      <c r="BH32" s="10" t="n"/>
       <c r="BI32" s="10" t="n"/>
-      <c r="BJ32" s="11" t="n"/>
-      <c r="BK32" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BJ32" s="10" t="n"/>
+      <c r="BK32" s="10" t="n"/>
       <c r="BL32" s="10" t="n"/>
       <c r="BM32" s="10" t="n"/>
       <c r="BN32" s="10" t="n"/>
@@ -10335,74 +10278,161 @@
       <c r="BP32" s="10" t="n"/>
       <c r="BQ32" s="11" t="n"/>
     </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>Kiểm tra dữ liệu nhập (Input Validation)</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n"/>
+    <row r="33" ht="176" customHeight="1">
+      <c r="A33" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-018</t>
+        </is>
+      </c>
       <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>Kiểm tra required khi chưa chọn JA đối tượng</t>
+        </is>
+      </c>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA</t>
+        </is>
+      </c>
       <c r="K33" s="10" t="n"/>
       <c r="L33" s="10" t="n"/>
       <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
-      <c r="P33" s="10" t="n"/>
-      <c r="Q33" s="10" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Không thêm JA đối tượng nào, chỉ nhập file và ngày dự định xóa rồi click「アップロード実行」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Gửi trực tiếp POST `/api/v1/file-upload` ở trạng thái JA đối tượng để trống bằng DevTools</t>
+          </r>
+        </is>
+      </c>
       <c r="R33" s="10" t="n"/>
       <c r="S33" s="10" t="n"/>
       <c r="T33" s="10" t="n"/>
       <c r="U33" s="10" t="n"/>
       <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n"/>
-      <c r="X33" s="10" t="n"/>
+      <c r="W33" s="11" t="n"/>
+      <c r="X33" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Hiển thị lỗi required (message `必須項目です。`, ACSMS-MSG-023-001)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Trả về HTTP 400 (`error_code: TARGET_JA_REQUIRED`, message `対象JAを1つ以上選択してください。`)</t>
+          </r>
+        </is>
+      </c>
       <c r="Y33" s="10" t="n"/>
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="10" t="n"/>
       <c r="AC33" s="10" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="10" t="n"/>
-      <c r="AF33" s="10" t="n"/>
-      <c r="AG33" s="10" t="n"/>
+      <c r="AD33" s="11" t="n"/>
+      <c r="AE33" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF33" s="11" t="n"/>
+      <c r="AG33" s="45" t="inlineStr"/>
       <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="10" t="n"/>
-      <c r="AJ33" s="10" t="n"/>
+      <c r="AI33" s="11" t="n"/>
+      <c r="AJ33" s="45" t="inlineStr"/>
       <c r="AK33" s="10" t="n"/>
-      <c r="AL33" s="10" t="n"/>
-      <c r="AM33" s="10" t="n"/>
+      <c r="AL33" s="11" t="n"/>
+      <c r="AM33" s="45" t="inlineStr"/>
       <c r="AN33" s="10" t="n"/>
-      <c r="AO33" s="10" t="n"/>
-      <c r="AP33" s="10" t="n"/>
+      <c r="AO33" s="11" t="n"/>
+      <c r="AP33" s="45" t="inlineStr"/>
       <c r="AQ33" s="10" t="n"/>
-      <c r="AR33" s="10" t="n"/>
-      <c r="AS33" s="10" t="n"/>
+      <c r="AR33" s="11" t="n"/>
+      <c r="AS33" s="45" t="inlineStr"/>
       <c r="AT33" s="10" t="n"/>
-      <c r="AU33" s="10" t="n"/>
-      <c r="AV33" s="10" t="n"/>
+      <c r="AU33" s="11" t="n"/>
+      <c r="AV33" s="45" t="inlineStr"/>
       <c r="AW33" s="10" t="n"/>
-      <c r="AX33" s="10" t="n"/>
-      <c r="AY33" s="10" t="n"/>
+      <c r="AX33" s="11" t="n"/>
+      <c r="AY33" s="45" t="inlineStr"/>
       <c r="AZ33" s="10" t="n"/>
-      <c r="BA33" s="10" t="n"/>
-      <c r="BB33" s="10" t="n"/>
+      <c r="BA33" s="11" t="n"/>
+      <c r="BB33" s="45" t="inlineStr"/>
       <c r="BC33" s="10" t="n"/>
-      <c r="BD33" s="10" t="n"/>
-      <c r="BE33" s="10" t="n"/>
+      <c r="BD33" s="11" t="n"/>
+      <c r="BE33" s="45" t="inlineStr"/>
       <c r="BF33" s="10" t="n"/>
-      <c r="BG33" s="10" t="n"/>
-      <c r="BH33" s="10" t="n"/>
+      <c r="BG33" s="11" t="n"/>
+      <c r="BH33" s="45" t="inlineStr"/>
       <c r="BI33" s="10" t="n"/>
-      <c r="BJ33" s="10" t="n"/>
-      <c r="BK33" s="10" t="n"/>
+      <c r="BJ33" s="11" t="n"/>
+      <c r="BK33" s="46" t="inlineStr"/>
       <c r="BL33" s="10" t="n"/>
       <c r="BM33" s="10" t="n"/>
       <c r="BN33" s="10" t="n"/>
@@ -10423,7 +10453,7 @@
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="46" t="inlineStr">
         <is>
-          <t>Kiểm tra required khi chưa chọn JA đối tượng</t>
+          <t>Kiểm tra thêm trùng cùng một JA</t>
         </is>
       </c>
       <c r="F34" s="10" t="n"/>
@@ -10458,7 +10488,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Không thêm JA đối tượng nào, chỉ nhập file và ngày dự định xóa rồi click「アップロード実行」
+            <t xml:space="preserve">Chọn 1 JA ở JA đối tượng và click button「追加」
 </t>
           </r>
           <r>
@@ -10475,7 +10505,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gửi trực tiếp POST `/api/v1/file-upload` ở trạng thái JA đối tượng để trống bằng DevTools</t>
+            <t>Chọn lại cùng một JA và click button「追加」</t>
           </r>
         </is>
       </c>
@@ -10501,7 +10531,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Hiển thị lỗi required (message `必須項目です。`, ACSMS-MSG-023-001)
+            <t xml:space="preserve">・JA đã chọn được thêm vào danh sách JA (JA code + JA name)
 </t>
           </r>
           <r>
@@ -10518,7 +10548,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Trả về HTTP 400 (`error_code: TARGET_JA_REQUIRED`, message `対象JAを1つ以上選択してください。`)</t>
+            <t xml:space="preserve">・Error message `このJAは既に選択されています。`（ACSMS-MSG-023-004）được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Dữ liệu trùng không được thêm vào danh sách JA</t>
           </r>
         </is>
       </c>
@@ -10572,7 +10610,7 @@
       <c r="BP34" s="10" t="n"/>
       <c r="BQ34" s="11" t="n"/>
     </row>
-    <row r="35" ht="176" customHeight="1">
+    <row r="35" ht="96" customHeight="1">
       <c r="A35" s="44" t="n">
         <v>20</v>
       </c>
@@ -10585,7 +10623,7 @@
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="46" t="inlineStr">
         <is>
-          <t>Kiểm tra thêm trùng cùng một JA</t>
+          <t>Kiểm tra required khi chưa chọn file</t>
         </is>
       </c>
       <c r="F35" s="10" t="n"/>
@@ -10620,24 +10658,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn 1 JA ở JA đối tượng và click button「追加」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Chọn lại cùng một JA và click button「追加」</t>
+            <t>Chỉ nhập JA đối tượng và ngày dự định xóa, không chọn file nào rồi click「アップロード実行」</t>
           </r>
         </is>
       </c>
@@ -10663,32 +10684,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・JA đã chọn được thêm vào danh sách JA (JA code + JA name)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Error message `このJAは既に選択されています。`（ACSMS-MSG-023-004）được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Dữ liệu trùng không được thêm vào danh sách JA</t>
+            <t xml:space="preserve">・Hiển thị lỗi required (message `必須項目です。`, ACSMS-MSG-023-001)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Xử lý upload không được thực thi</t>
           </r>
         </is>
       </c>
@@ -10755,7 +10759,7 @@
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="46" t="inlineStr">
         <is>
-          <t>Kiểm tra required khi chưa chọn file</t>
+          <t>Kiểm tra required khi chưa nhập ngày dự định xóa</t>
         </is>
       </c>
       <c r="F36" s="10" t="n"/>
@@ -10790,7 +10794,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chỉ nhập JA đối tượng và ngày dự định xóa, không chọn file nào rồi click「アップロード実行」</t>
+            <t>Chỉ nhập JA đối tượng và file, để trống ngày dự định xóa rồi click「アップロード実行」</t>
           </r>
         </is>
       </c>
@@ -10878,7 +10882,7 @@
       <c r="BP36" s="10" t="n"/>
       <c r="BQ36" s="11" t="n"/>
     </row>
-    <row r="37" ht="96" customHeight="1">
+    <row r="37" ht="80" customHeight="1">
       <c r="A37" s="44" t="n">
         <v>22</v>
       </c>
@@ -10891,7 +10895,7 @@
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="46" t="inlineStr">
         <is>
-          <t>Kiểm tra required khi chưa nhập ngày dự định xóa</t>
+          <t>Chọn ngày quá khứ cho ngày dự định xóa (không cho phép)</t>
         </is>
       </c>
       <c r="F37" s="10" t="n"/>
@@ -10926,7 +10930,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chỉ nhập JA đối tượng và file, để trống ngày dự định xóa rồi click「アップロード実行」</t>
+            <t>Chọn ngày quá khứ (ngày hôm trước) trên calendar ngày dự định xóa</t>
           </r>
         </is>
       </c>
@@ -10952,15 +10956,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Hiển thị lỗi required (message `必須項目です。`, ACSMS-MSG-023-001)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Xử lý upload không được thực thi</t>
+            <t>・Không thể chọn ngày quá khứ (ngày quá khứ ở trạng thái disable trên calendar, hoặc phát sinh lỗi khi chọn)</t>
           </r>
         </is>
       </c>
@@ -11014,7 +11010,7 @@
       <c r="BP37" s="10" t="n"/>
       <c r="BQ37" s="11" t="n"/>
     </row>
-    <row r="38" ht="80" customHeight="1">
+    <row r="38" ht="96" customHeight="1">
       <c r="A38" s="44" t="n">
         <v>23</v>
       </c>
@@ -11027,7 +11023,7 @@
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="46" t="inlineStr">
         <is>
-          <t>Chọn ngày quá khứ cho ngày dự định xóa (không cho phép)</t>
+          <t>Chọn ngày hôm nay cho ngày dự định xóa (giá trị biên・cho phép)</t>
         </is>
       </c>
       <c r="F38" s="10" t="n"/>
@@ -11062,7 +11058,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chọn ngày quá khứ (ngày hôm trước) trên calendar ngày dự định xóa</t>
+            <t>Chọn ngày hôm nay trên calendar ngày dự định xóa</t>
           </r>
         </is>
       </c>
@@ -11088,7 +11084,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Không thể chọn ngày quá khứ (ngày quá khứ ở trạng thái disable trên calendar, hoặc phát sinh lỗi khi chọn)</t>
+            <t>・Có thể chọn ngày hôm nay (được cho phép như giá trị biên)</t>
           </r>
         </is>
       </c>
@@ -11100,7 +11096,7 @@
       <c r="AD38" s="11" t="n"/>
       <c r="AE38" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AF38" s="11" t="n"/>
@@ -11134,7 +11130,11 @@
       <c r="BH38" s="45" t="inlineStr"/>
       <c r="BI38" s="10" t="n"/>
       <c r="BJ38" s="11" t="n"/>
-      <c r="BK38" s="46" t="inlineStr"/>
+      <c r="BK38" s="46" t="inlineStr">
+        <is>
+          <t>Giá trị biên của không cho phép ngày quá khứ (ngày hôm nay được cho phép). Cần xác nhận với khách hàng về việc xử lý ngày hôm nay để kiểm tra giá trị biên theo spec.</t>
+        </is>
+      </c>
       <c r="BL38" s="10" t="n"/>
       <c r="BM38" s="10" t="n"/>
       <c r="BN38" s="10" t="n"/>
@@ -11142,7 +11142,7 @@
       <c r="BP38" s="10" t="n"/>
       <c r="BQ38" s="11" t="n"/>
     </row>
-    <row r="39" ht="96" customHeight="1">
+    <row r="39" ht="208" customHeight="1">
       <c r="A39" s="44" t="n">
         <v>24</v>
       </c>
@@ -11155,7 +11155,7 @@
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="46" t="inlineStr">
         <is>
-          <t>Chọn ngày hôm nay cho ngày dự định xóa (giá trị biên・cho phép)</t>
+          <t>File size vượt quá 30MB</t>
         </is>
       </c>
       <c r="F39" s="10" t="n"/>
@@ -11165,7 +11165,8 @@
       <c r="J39" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
+・Đã đăng nhập + đã xác thực MFA
+・Chuẩn bị file test có size vượt quá 30MB</t>
         </is>
       </c>
       <c r="K39" s="10" t="n"/>
@@ -11190,7 +11191,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chọn ngày hôm nay trên calendar ngày dự định xóa</t>
+            <t xml:space="preserve">Chọn file vượt quá 30MB
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Gửi trực tiếp POST `/api/v1/file-upload` có chứa file vượt quá 30MB bằng DevTools</t>
           </r>
         </is>
       </c>
@@ -11216,7 +11234,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Có thể chọn ngày hôm nay (được cho phép như giá trị biên)</t>
+            <t xml:space="preserve">・Error message `ファイルサイズが30MBを超えています。({fileName})`（ACSMS-MSG-023-002）được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・File đó không được thêm vào danh sách file
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Trả về HTTP 400 (`error_code: FILE_SIZE_EXCEEDED`, message `ファイルサイズが30MBを超えています。`)</t>
           </r>
         </is>
       </c>
@@ -11228,7 +11271,7 @@
       <c r="AD39" s="11" t="n"/>
       <c r="AE39" s="45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF39" s="11" t="n"/>
@@ -11262,11 +11305,7 @@
       <c r="BH39" s="45" t="inlineStr"/>
       <c r="BI39" s="10" t="n"/>
       <c r="BJ39" s="11" t="n"/>
-      <c r="BK39" s="46" t="inlineStr">
-        <is>
-          <t>Giá trị biên của không cho phép ngày quá khứ (ngày hôm nay được cho phép). Cần xác nhận với khách hàng về việc xử lý ngày hôm nay để kiểm tra giá trị biên theo spec.</t>
-        </is>
-      </c>
+      <c r="BK39" s="46" t="inlineStr"/>
       <c r="BL39" s="10" t="n"/>
       <c r="BM39" s="10" t="n"/>
       <c r="BN39" s="10" t="n"/>
@@ -11274,7 +11313,7 @@
       <c r="BP39" s="10" t="n"/>
       <c r="BQ39" s="11" t="n"/>
     </row>
-    <row r="40" ht="208" customHeight="1">
+    <row r="40" ht="96" customHeight="1">
       <c r="A40" s="44" t="n">
         <v>25</v>
       </c>
@@ -11287,7 +11326,7 @@
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="46" t="inlineStr">
         <is>
-          <t>File size vượt quá 30MB</t>
+          <t>File size đúng 30MB (giá trị biên・cho phép)</t>
         </is>
       </c>
       <c r="F40" s="10" t="n"/>
@@ -11298,7 +11337,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã đăng nhập + đã xác thực MFA
-・Chuẩn bị file test có size vượt quá 30MB</t>
+・Chuẩn bị file test có size đúng 30MB (30×1024×1024 byte)</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
@@ -11323,24 +11362,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn file vượt quá 30MB
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Gửi trực tiếp POST `/api/v1/file-upload` có chứa file vượt quá 30MB bằng DevTools</t>
+            <t>Chọn file đúng 30MB</t>
           </r>
         </is>
       </c>
@@ -11366,32 +11388,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Error message `ファイルサイズが30MBを超えています。({fileName})`（ACSMS-MSG-023-002）được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・File đó không được thêm vào danh sách file
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Trả về HTTP 400 (`error_code: FILE_SIZE_EXCEEDED`, message `ファイルサイズが30MBを超えています。`)</t>
+            <t>・File được thêm vào danh sách file (được cho phép như giá trị biên)</t>
           </r>
         </is>
       </c>
@@ -11403,7 +11400,7 @@
       <c r="AD40" s="11" t="n"/>
       <c r="AE40" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AF40" s="11" t="n"/>
@@ -11445,7 +11442,7 @@
       <c r="BP40" s="10" t="n"/>
       <c r="BQ40" s="11" t="n"/>
     </row>
-    <row r="41" ht="96" customHeight="1">
+    <row r="41" ht="128" customHeight="1">
       <c r="A41" s="44" t="n">
         <v>26</v>
       </c>
@@ -11458,7 +11455,7 @@
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="46" t="inlineStr">
         <is>
-          <t>File size đúng 30MB (giá trị biên・cho phép)</t>
+          <t>Chấp nhận file định dạng được cho phép</t>
         </is>
       </c>
       <c r="F41" s="10" t="n"/>
@@ -11469,7 +11466,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã đăng nhập + đã xác thực MFA
-・Chuẩn bị file test có size đúng 30MB (30×1024×1024 byte)</t>
+・Chuẩn bị file test của mỗi extension được cho phép (.xlsx, .xls, .pdf, .jpg, .jpeg, .png, .doc, .docx, .pptx, .ppt, .csv, .txt, .zip)</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
@@ -11494,7 +11491,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chọn file đúng 30MB</t>
+            <t>Chọn lần lượt các file có extension được cho phép</t>
           </r>
         </is>
       </c>
@@ -11520,7 +11517,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・File được thêm vào danh sách file (được cho phép như giá trị biên)</t>
+            <t>・File có extension được cho phép (Excel／PDF／hình ảnh／Word／PowerPoint／CSV／text／nén) được thêm vào danh sách file</t>
           </r>
         </is>
       </c>
@@ -11532,7 +11529,7 @@
       <c r="AD41" s="11" t="n"/>
       <c r="AE41" s="45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF41" s="11" t="n"/>
@@ -11574,7 +11571,7 @@
       <c r="BP41" s="10" t="n"/>
       <c r="BQ41" s="11" t="n"/>
     </row>
-    <row r="42" ht="128" customHeight="1">
+    <row r="42" ht="208" customHeight="1">
       <c r="A42" s="44" t="n">
         <v>27</v>
       </c>
@@ -11587,7 +11584,7 @@
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>Chấp nhận file định dạng được cho phép</t>
+          <t>Từ chối file định dạng không được cho phép</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -11598,7 +11595,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã đăng nhập + đã xác thực MFA
-・Chuẩn bị file test của mỗi extension được cho phép (.xlsx, .xls, .pdf, .jpg, .jpeg, .png, .doc, .docx, .pptx, .ppt, .csv, .txt, .zip)</t>
+・Chuẩn bị file test có extension không được cho phép (.exe)</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
@@ -11623,7 +11620,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chọn lần lượt các file có extension được cho phép</t>
+            <t xml:space="preserve">Chọn file có extension không được cho phép (.exe)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Gửi trực tiếp POST `/api/v1/file-upload` có chứa file extension không được cho phép bằng DevTools</t>
           </r>
         </is>
       </c>
@@ -11649,7 +11663,32 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・File có extension được cho phép (Excel／PDF／hình ảnh／Word／PowerPoint／CSV／text／nén) được thêm vào danh sách file</t>
+            <t xml:space="preserve">・Error message `許可されていないファイル形式です。({fileName})`（ACSMS-MSG-023-010）được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・File đó không được thêm vào danh sách file
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Trả về HTTP 400 (`error_code: FILE_FORMAT_ERROR`, message `許可されていないファイル形式です。`)</t>
           </r>
         </is>
       </c>
@@ -11661,7 +11700,7 @@
       <c r="AD42" s="11" t="n"/>
       <c r="AE42" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF42" s="11" t="n"/>
@@ -11703,7 +11742,7 @@
       <c r="BP42" s="10" t="n"/>
       <c r="BQ42" s="11" t="n"/>
     </row>
-    <row r="43" ht="208" customHeight="1">
+    <row r="43" ht="96" customHeight="1">
       <c r="A43" s="44" t="n">
         <v>28</v>
       </c>
@@ -11716,7 +11755,7 @@
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="46" t="inlineStr">
         <is>
-          <t>Từ chối file định dạng không được cho phép</t>
+          <t>Chấp nhận extension chữ hoa (phán định bằng chuyển thành chữ thường)</t>
         </is>
       </c>
       <c r="F43" s="10" t="n"/>
@@ -11727,7 +11766,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã đăng nhập + đã xác thực MFA
-・Chuẩn bị file test có extension không được cho phép (.exe)</t>
+・Chuẩn bị file test có extension chữ hoa (`IMG.JPG`)</t>
         </is>
       </c>
       <c r="K43" s="10" t="n"/>
@@ -11752,24 +11791,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn file có extension không được cho phép (.exe)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Gửi trực tiếp POST `/api/v1/file-upload` có chứa file extension không được cho phép bằng DevTools</t>
+            <t>Chọn file có extension chữ hoa (`IMG.JPG`)</t>
           </r>
         </is>
       </c>
@@ -11795,32 +11817,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Error message `許可されていないファイル形式です。({fileName})`（ACSMS-MSG-023-010）được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・File đó không được thêm vào danh sách file
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Trả về HTTP 400 (`error_code: FILE_FORMAT_ERROR`, message `許可されていないファイル形式です。`)</t>
+            <t>・File được thêm vào danh sách file (do extension được phán định sau khi chuyển thành chữ thường, nên `.JPG` cũng được cho phép)</t>
           </r>
         </is>
       </c>
@@ -11832,7 +11829,7 @@
       <c r="AD43" s="11" t="n"/>
       <c r="AE43" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AF43" s="11" t="n"/>
@@ -11874,7 +11871,7 @@
       <c r="BP43" s="10" t="n"/>
       <c r="BQ43" s="11" t="n"/>
     </row>
-    <row r="44" ht="96" customHeight="1">
+    <row r="44" ht="144" customHeight="1">
       <c r="A44" s="44" t="n">
         <v>29</v>
       </c>
@@ -11887,7 +11884,7 @@
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="46" t="inlineStr">
         <is>
-          <t>Chấp nhận extension chữ hoa (phán định bằng chuyển thành chữ thường)</t>
+          <t>Chọn nhiều file và hiển thị định dạng tên file</t>
         </is>
       </c>
       <c r="F44" s="10" t="n"/>
@@ -11897,8 +11894,7 @@
       <c r="J44" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA
-・Chuẩn bị file test có extension chữ hoa (`IMG.JPG`)</t>
+・Đã đăng nhập + đã xác thực MFA</t>
         </is>
       </c>
       <c r="K44" s="10" t="n"/>
@@ -11923,7 +11919,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chọn file có extension chữ hoa (`IMG.JPG`)</t>
+            <t xml:space="preserve">Chọn đồng thời nhiều file
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Sau khi upload, xác nhận định dạng hiển thị tên file của「アップロードされたファイルリスト」</t>
           </r>
         </is>
       </c>
@@ -11949,7 +11962,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・File được thêm vào danh sách file (do extension được phán định sau khi chuyển thành chữ thường, nên `.JPG` cũng được cho phép)</t>
+            <t xml:space="preserve">・Tất cả nhiều file đều được thêm vào danh sách file (tên file + size)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Tên file được hiển thị theo định dạng「yyyymmddJaIDRole_tên file」</t>
           </r>
         </is>
       </c>
@@ -11961,7 +11991,7 @@
       <c r="AD44" s="11" t="n"/>
       <c r="AE44" s="45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF44" s="11" t="n"/>
@@ -11995,7 +12025,12 @@
       <c r="BH44" s="45" t="inlineStr"/>
       <c r="BI44" s="10" t="n"/>
       <c r="BJ44" s="11" t="n"/>
-      <c r="BK44" s="46" t="inlineStr"/>
+      <c r="BK44" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL44" s="10" t="n"/>
       <c r="BM44" s="10" t="n"/>
       <c r="BN44" s="10" t="n"/>
@@ -12003,166 +12038,74 @@
       <c r="BP44" s="10" t="n"/>
       <c r="BQ44" s="11" t="n"/>
     </row>
-    <row r="45" ht="144" customHeight="1">
-      <c r="A45" s="44" t="n">
-        <v>30</v>
-      </c>
-      <c r="B45" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-030</t>
-        </is>
-      </c>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>Nghiệp vụ — Upload (Function — Upload)</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
       <c r="C45" s="10" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="46" t="inlineStr">
-        <is>
-          <t>Chọn nhiều file và hiển thị định dạng tên file</t>
-        </is>
-      </c>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="10" t="n"/>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
-        </is>
-      </c>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="10" t="n"/>
       <c r="M45" s="10" t="n"/>
       <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
-      <c r="P45" s="11" t="n"/>
-      <c r="Q45" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Chọn đồng thời nhiều file
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Sau khi upload, xác nhận định dạng hiển thị tên file của「アップロードされたファイルリスト」</t>
-          </r>
-        </is>
-      </c>
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n"/>
       <c r="R45" s="10" t="n"/>
       <c r="S45" s="10" t="n"/>
       <c r="T45" s="10" t="n"/>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
-      <c r="W45" s="11" t="n"/>
-      <c r="X45" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Tất cả nhiều file đều được thêm vào danh sách file (tên file + size)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Tên file được hiển thị theo định dạng「yyyymmddJaIDRole_tên file」</t>
-          </r>
-        </is>
-      </c>
+      <c r="W45" s="10" t="n"/>
+      <c r="X45" s="10" t="n"/>
       <c r="Y45" s="10" t="n"/>
       <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="10" t="n"/>
       <c r="AB45" s="10" t="n"/>
       <c r="AC45" s="10" t="n"/>
-      <c r="AD45" s="11" t="n"/>
-      <c r="AE45" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF45" s="11" t="n"/>
-      <c r="AG45" s="45" t="inlineStr"/>
+      <c r="AD45" s="10" t="n"/>
+      <c r="AE45" s="10" t="n"/>
+      <c r="AF45" s="10" t="n"/>
+      <c r="AG45" s="10" t="n"/>
       <c r="AH45" s="10" t="n"/>
-      <c r="AI45" s="11" t="n"/>
-      <c r="AJ45" s="45" t="inlineStr"/>
+      <c r="AI45" s="10" t="n"/>
+      <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="10" t="n"/>
-      <c r="AL45" s="11" t="n"/>
-      <c r="AM45" s="45" t="inlineStr"/>
+      <c r="AL45" s="10" t="n"/>
+      <c r="AM45" s="10" t="n"/>
       <c r="AN45" s="10" t="n"/>
-      <c r="AO45" s="11" t="n"/>
-      <c r="AP45" s="45" t="inlineStr"/>
+      <c r="AO45" s="10" t="n"/>
+      <c r="AP45" s="10" t="n"/>
       <c r="AQ45" s="10" t="n"/>
-      <c r="AR45" s="11" t="n"/>
-      <c r="AS45" s="45" t="inlineStr"/>
+      <c r="AR45" s="10" t="n"/>
+      <c r="AS45" s="10" t="n"/>
       <c r="AT45" s="10" t="n"/>
-      <c r="AU45" s="11" t="n"/>
-      <c r="AV45" s="45" t="inlineStr"/>
+      <c r="AU45" s="10" t="n"/>
+      <c r="AV45" s="10" t="n"/>
       <c r="AW45" s="10" t="n"/>
-      <c r="AX45" s="11" t="n"/>
-      <c r="AY45" s="45" t="inlineStr"/>
+      <c r="AX45" s="10" t="n"/>
+      <c r="AY45" s="10" t="n"/>
       <c r="AZ45" s="10" t="n"/>
-      <c r="BA45" s="11" t="n"/>
-      <c r="BB45" s="45" t="inlineStr"/>
+      <c r="BA45" s="10" t="n"/>
+      <c r="BB45" s="10" t="n"/>
       <c r="BC45" s="10" t="n"/>
-      <c r="BD45" s="11" t="n"/>
-      <c r="BE45" s="45" t="inlineStr"/>
+      <c r="BD45" s="10" t="n"/>
+      <c r="BE45" s="10" t="n"/>
       <c r="BF45" s="10" t="n"/>
-      <c r="BG45" s="11" t="n"/>
-      <c r="BH45" s="45" t="inlineStr"/>
+      <c r="BG45" s="10" t="n"/>
+      <c r="BH45" s="10" t="n"/>
       <c r="BI45" s="10" t="n"/>
-      <c r="BJ45" s="11" t="n"/>
-      <c r="BK45" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BJ45" s="10" t="n"/>
+      <c r="BK45" s="10" t="n"/>
       <c r="BL45" s="10" t="n"/>
       <c r="BM45" s="10" t="n"/>
       <c r="BN45" s="10" t="n"/>
@@ -12170,74 +12113,236 @@
       <c r="BP45" s="10" t="n"/>
       <c r="BQ45" s="11" t="n"/>
     </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="32" t="inlineStr">
-        <is>
-          <t>Nghiệp vụ — Upload (Function — Upload)</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n"/>
+    <row r="46" ht="416" customHeight="1">
+      <c r="A46" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="B46" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-030</t>
+        </is>
+      </c>
       <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="46" t="inlineStr">
+        <is>
+          <t>Upload luồng bình thường (1 JA × 1 file)</t>
+        </is>
+      </c>
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="10" t="n"/>
       <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA</t>
+        </is>
+      </c>
       <c r="K46" s="10" t="n"/>
       <c r="L46" s="10" t="n"/>
       <c r="M46" s="10" t="n"/>
       <c r="N46" s="10" t="n"/>
       <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
+      <c r="P46" s="11" t="n"/>
+      <c r="Q46" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thêm 1 JA đối tượng, chọn 1 file định dạng được cho phép, nhập ngày dự định xóa từ hôm nay trở đi
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Click「アップロード実行」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Click「OK」trên dialog xác nhận</t>
+          </r>
+        </is>
+      </c>
       <c r="R46" s="10" t="n"/>
       <c r="S46" s="10" t="n"/>
       <c r="T46" s="10" t="n"/>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
+      <c r="W46" s="11" t="n"/>
+      <c r="X46" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・JA đối tượng và file được hiển thị trong danh sách
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `このファイルをアップロードしますか？`, ACSMS-MSG-023-008)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Trả về HTTP 202
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Success message `ファイルのアップロードが完了しました。`（ACSMS-MSG-023-006）được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Form (JA đối tượng・file・ngày dự định xóa) được clear
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「アップロードされたファイルリスト」được fetch lại, và row mới được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Badge「未送信」hoặc「送信中」được hiển thị ở cột「通知ステータス」của row mới</t>
+          </r>
+        </is>
+      </c>
       <c r="Y46" s="10" t="n"/>
       <c r="Z46" s="10" t="n"/>
       <c r="AA46" s="10" t="n"/>
       <c r="AB46" s="10" t="n"/>
       <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
+      <c r="AD46" s="11" t="n"/>
+      <c r="AE46" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF46" s="11" t="n"/>
+      <c r="AG46" s="45" t="inlineStr"/>
       <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
+      <c r="AI46" s="11" t="n"/>
+      <c r="AJ46" s="45" t="inlineStr"/>
       <c r="AK46" s="10" t="n"/>
-      <c r="AL46" s="10" t="n"/>
-      <c r="AM46" s="10" t="n"/>
+      <c r="AL46" s="11" t="n"/>
+      <c r="AM46" s="45" t="inlineStr"/>
       <c r="AN46" s="10" t="n"/>
-      <c r="AO46" s="10" t="n"/>
-      <c r="AP46" s="10" t="n"/>
+      <c r="AO46" s="11" t="n"/>
+      <c r="AP46" s="45" t="inlineStr"/>
       <c r="AQ46" s="10" t="n"/>
-      <c r="AR46" s="10" t="n"/>
-      <c r="AS46" s="10" t="n"/>
+      <c r="AR46" s="11" t="n"/>
+      <c r="AS46" s="45" t="inlineStr"/>
       <c r="AT46" s="10" t="n"/>
-      <c r="AU46" s="10" t="n"/>
-      <c r="AV46" s="10" t="n"/>
+      <c r="AU46" s="11" t="n"/>
+      <c r="AV46" s="45" t="inlineStr"/>
       <c r="AW46" s="10" t="n"/>
-      <c r="AX46" s="10" t="n"/>
-      <c r="AY46" s="10" t="n"/>
+      <c r="AX46" s="11" t="n"/>
+      <c r="AY46" s="45" t="inlineStr"/>
       <c r="AZ46" s="10" t="n"/>
-      <c r="BA46" s="10" t="n"/>
-      <c r="BB46" s="10" t="n"/>
+      <c r="BA46" s="11" t="n"/>
+      <c r="BB46" s="45" t="inlineStr"/>
       <c r="BC46" s="10" t="n"/>
-      <c r="BD46" s="10" t="n"/>
-      <c r="BE46" s="10" t="n"/>
+      <c r="BD46" s="11" t="n"/>
+      <c r="BE46" s="45" t="inlineStr"/>
       <c r="BF46" s="10" t="n"/>
-      <c r="BG46" s="10" t="n"/>
-      <c r="BH46" s="10" t="n"/>
+      <c r="BG46" s="11" t="n"/>
+      <c r="BH46" s="45" t="inlineStr"/>
       <c r="BI46" s="10" t="n"/>
-      <c r="BJ46" s="10" t="n"/>
-      <c r="BK46" s="10" t="n"/>
+      <c r="BJ46" s="11" t="n"/>
+      <c r="BK46" s="46" t="inlineStr"/>
       <c r="BL46" s="10" t="n"/>
       <c r="BM46" s="10" t="n"/>
       <c r="BN46" s="10" t="n"/>
@@ -12245,7 +12350,7 @@
       <c r="BP46" s="10" t="n"/>
       <c r="BQ46" s="11" t="n"/>
     </row>
-    <row r="47" ht="416" customHeight="1">
+    <row r="47" ht="208" customHeight="1">
       <c r="A47" s="44" t="n">
         <v>31</v>
       </c>
@@ -12258,7 +12363,7 @@
       <c r="D47" s="11" t="n"/>
       <c r="E47" s="46" t="inlineStr">
         <is>
-          <t>Upload luồng bình thường (1 JA × 1 file)</t>
+          <t>Tạo N×M record (nhiều JA × nhiều file)</t>
         </is>
       </c>
       <c r="F47" s="10" t="n"/>
@@ -12293,7 +12398,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thêm 1 JA đối tượng, chọn 1 file định dạng được cho phép, nhập ngày dự định xóa từ hôm nay trở đi
+            <t xml:space="preserve">Thêm 2 JA đối tượng, chọn 2 file định dạng được cho phép, nhập ngày dự định xóa rồi click「アップロード実行」→「OK」
 </t>
           </r>
           <r>
@@ -12310,24 +12415,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Click「アップロード実行」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Click「OK」trên dialog xác nhận</t>
+            <t>Xác nhận DB: `SELECT ja_id, file_name FROM t_file_upload WHERE created_by = :account_id ORDER BY file_upload_id DESC LIMIT 4`</t>
           </r>
         </is>
       </c>
@@ -12353,7 +12441,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・JA đối tượng và file được hiển thị trong danh sách
+            <t xml:space="preserve">・Trả về HTTP 202
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Success message `ファイルのアップロードが完了しました。`（ACSMS-MSG-023-006）được hiển thị
 </t>
           </r>
           <r>
@@ -12370,65 +12466,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `このファイルをアップロードしますか？`, ACSMS-MSG-023-008)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Trả về HTTP 202
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Success message `ファイルのアップロードが完了しました。`（ACSMS-MSG-023-006）được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Form (JA đối tượng・file・ngày dự định xóa) được clear
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・「アップロードされたファイルリスト」được fetch lại, và row mới được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Badge「未送信」hoặc「送信中」được hiển thị ở cột「通知ステータス」của row mới</t>
+            <t>・N×M = 2×2 = 4 record được đăng ký vào `t_file_upload` (tổ hợp của mỗi JA × mỗi file)</t>
           </r>
         </is>
       </c>
@@ -12482,7 +12520,7 @@
       <c r="BP47" s="10" t="n"/>
       <c r="BQ47" s="11" t="n"/>
     </row>
-    <row r="48" ht="208" customHeight="1">
+    <row r="48" ht="192" customHeight="1">
       <c r="A48" s="44" t="n">
         <v>32</v>
       </c>
@@ -12495,7 +12533,7 @@
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="46" t="inlineStr">
         <is>
-          <t>Tạo N×M record (nhiều JA × nhiều file)</t>
+          <t>Chọn toàn bộ JA (record có ja_id=NULL)</t>
         </is>
       </c>
       <c r="F48" s="10" t="n"/>
@@ -12530,7 +12568,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thêm 2 JA đối tượng, chọn 2 file định dạng được cho phép, nhập ngày dự định xóa rồi click「アップロード実行」→「OK」
+            <t xml:space="preserve">Chọn「全JA」ở JA đối tượng và thêm vào, chọn 1 file, nhập ngày dự định xóa rồi click「アップロード実行」→「OK」
 </t>
           </r>
           <r>
@@ -12547,7 +12585,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận DB: `SELECT ja_id, file_name FROM t_file_upload WHERE created_by = :account_id ORDER BY file_upload_id DESC LIMIT 4`</t>
+            <t>Xác nhận DB: `SELECT ja_id FROM t_file_upload WHERE created_by = :account_id ORDER BY file_upload_id DESC LIMIT 1`</t>
           </r>
         </is>
       </c>
@@ -12579,14 +12617,6 @@
           <r>
             <rPr>
               <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Success message `ファイルのアップロードが完了しました。`（ACSMS-MSG-023-006）được hiển thị
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
               <b val="1"/>
               <sz val="10"/>
             </rPr>
@@ -12598,7 +12628,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・N×M = 2×2 = 4 record được đăng ký vào `t_file_upload` (tổ hợp của mỗi JA × mỗi file)</t>
+            <t>・1 record có `ja_id` là NULL được đăng ký vào `t_file_upload`</t>
           </r>
         </is>
       </c>
@@ -12652,7 +12682,7 @@
       <c r="BP48" s="10" t="n"/>
       <c r="BQ48" s="11" t="n"/>
     </row>
-    <row r="49" ht="192" customHeight="1">
+    <row r="49" ht="208" customHeight="1">
       <c r="A49" s="44" t="n">
         <v>33</v>
       </c>
@@ -12665,7 +12695,7 @@
       <c r="D49" s="11" t="n"/>
       <c r="E49" s="46" t="inlineStr">
         <is>
-          <t>Chọn toàn bộ JA (record có ja_id=NULL)</t>
+          <t>Xác nhận persistence DB và status ban đầu</t>
         </is>
       </c>
       <c r="F49" s="10" t="n"/>
@@ -12700,7 +12730,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn「全JA」ở JA đối tượng và thêm vào, chọn 1 file, nhập ngày dự định xóa rồi click「アップロード実行」→「OK」
+            <t xml:space="preserve">Thực hiện upload (1 JA × 1 file)
 </t>
           </r>
           <r>
@@ -12717,7 +12747,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận DB: `SELECT ja_id FROM t_file_upload WHERE created_by = :account_id ORDER BY file_upload_id DESC LIMIT 1`</t>
+            <t>Xác nhận DB: `SELECT status, notification_status, scheduled_delete_date, error_file_path FROM t_file_upload WHERE file_upload_id = :new_id`</t>
           </r>
         </is>
       </c>
@@ -12760,7 +12790,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・1 record có `ja_id` là NULL được đăng ký vào `t_file_upload`</t>
+            <t xml:space="preserve">・Dữ liệu được đăng ký (`status = 1`（đang xử lý）, `notification_status = 1`（chưa gửi）, `error_file_path = ""`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`scheduled_delete_date` được đăng ký theo ngày dự định xóa đã chỉ định trên màn hình</t>
           </r>
         </is>
       </c>
@@ -12814,7 +12852,7 @@
       <c r="BP49" s="10" t="n"/>
       <c r="BQ49" s="11" t="n"/>
     </row>
-    <row r="50" ht="208" customHeight="1">
+    <row r="50" ht="176" customHeight="1">
       <c r="A50" s="44" t="n">
         <v>34</v>
       </c>
@@ -12827,7 +12865,7 @@
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="46" t="inlineStr">
         <is>
-          <t>Xác nhận persistence DB và status ban đầu</t>
+          <t>Record audit log (upload)</t>
         </is>
       </c>
       <c r="F50" s="10" t="n"/>
@@ -12862,7 +12900,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thực hiện upload (1 JA × 1 file)
+            <t xml:space="preserve">Thực hiện upload
 </t>
           </r>
           <r>
@@ -12879,7 +12917,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận DB: `SELECT status, notification_status, scheduled_delete_date, error_file_path FROM t_file_upload WHERE file_upload_id = :new_id`</t>
+            <t>Xác nhận DB: `SELECT log_type, operation, result_status, target_table, account_id FROM t_log WHERE target_table = 't_file_upload' ORDER BY log_datetime DESC LIMIT 1`</t>
           </r>
         </is>
       </c>
@@ -12922,15 +12960,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Dữ liệu được đăng ký (`status = 1`（đang xử lý）, `notification_status = 1`（chưa gửi）, `error_file_path = ""`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`scheduled_delete_date` được đăng ký theo ngày dự định xóa đã chỉ định trên màn hình</t>
+            <t xml:space="preserve">・Audit log được record (`log_type = 4`（thao tác file）, `operation = 'CREATE'`, `result_status = 1`, `target_table = 't_file_upload'`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・`account_id` khớp với account test</t>
           </r>
         </is>
       </c>
@@ -12984,7 +13022,7 @@
       <c r="BP50" s="10" t="n"/>
       <c r="BQ50" s="11" t="n"/>
     </row>
-    <row r="51" ht="176" customHeight="1">
+    <row r="51" ht="288" customHeight="1">
       <c r="A51" s="44" t="n">
         <v>35</v>
       </c>
@@ -12997,7 +13035,7 @@
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>Record audit log (upload)</t>
+          <t>Chuyển đổi badge trạng thái thông báo (bất đồng bộ)</t>
         </is>
       </c>
       <c r="F51" s="10" t="n"/>
@@ -13007,7 +13045,8 @@
       <c r="J51" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
+・Đã đăng nhập + đã xác thực MFA
+・Địa chỉ email nhận thông báo (`m_account.email` v.v.) đã được thiết lập cho JA đối tượng</t>
         </is>
       </c>
       <c r="K51" s="10" t="n"/>
@@ -13032,7 +13071,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thực hiện upload
+            <t xml:space="preserve">Thực hiện upload và xác nhận cột「通知ステータス」của「アップロードされたファイルリスト」
 </t>
           </r>
           <r>
@@ -13049,7 +13088,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận DB: `SELECT log_type, operation, result_status, target_table, account_id FROM t_log WHERE target_table = 't_file_upload' ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t>Sau một khoảng thời gian (sau khi background worker xử lý), reload màn hình và xác nhận lại cột「通知ステータス」</t>
           </r>
         </is>
       </c>
@@ -13075,7 +13114,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Trả về HTTP 202
+            <t xml:space="preserve">・Badge「未送信」hoặc「送信中」được hiển thị ở cột「通知ステータス」
 </t>
           </r>
           <r>
@@ -13092,15 +13131,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Audit log được record (`log_type = 4`（thao tác file）, `operation = 'CREATE'`, `result_status = 1`, `target_table = 't_file_upload'`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・`account_id` khớp với account test</t>
+            <t xml:space="preserve">・Sau khi gửi thành công tới toàn bộ địa chỉ,「通知ステータス」được cập nhật thành badge「完了」(`notification_status = 3`, `notified_at` được record)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Do việc gửi email được background worker thực thi bất đồng bộ, nên API trả về HTTP 202 ngay lập tức</t>
           </r>
         </is>
       </c>
@@ -13154,7 +13202,7 @@
       <c r="BP51" s="10" t="n"/>
       <c r="BQ51" s="11" t="n"/>
     </row>
-    <row r="52" ht="288" customHeight="1">
+    <row r="52" ht="272" customHeight="1">
       <c r="A52" s="44" t="n">
         <v>36</v>
       </c>
@@ -13167,7 +13215,7 @@
       <c r="D52" s="11" t="n"/>
       <c r="E52" s="46" t="inlineStr">
         <is>
-          <t>Chuyển đổi badge trạng thái thông báo (bất đồng bộ)</t>
+          <t>Gửi email thông báo thất bại tới một phần JA</t>
         </is>
       </c>
       <c r="F52" s="10" t="n"/>
@@ -13178,7 +13226,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã đăng nhập + đã xác thực MFA
-・Địa chỉ email nhận thông báo (`m_account.email` v.v.) đã được thiết lập cho JA đối tượng</t>
+・Chuẩn bị trạng thái trong nhiều JA có 1 JA có địa chỉ email không hợp lệ</t>
         </is>
       </c>
       <c r="K52" s="10" t="n"/>
@@ -13203,7 +13251,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thực hiện upload và xác nhận cột「通知ステータス」của「アップロードされたファイルリスト」
+            <t xml:space="preserve">Thực hiện upload nhắm tới nhiều JA (1 JA ở trạng thái gửi thất bại)
 </t>
           </r>
           <r>
@@ -13220,7 +13268,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Sau một khoảng thời gian (sau khi background worker xử lý), reload màn hình và xác nhận lại cột「通知ステータス」</t>
+            <t>Sau khi background worker xử lý, reload màn hình và xác nhận cột「通知ステータス」</t>
           </r>
         </is>
       </c>
@@ -13246,7 +13294,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Badge「未送信」hoặc「送信中」được hiển thị ở cột「通知ステータス」
+            <t xml:space="preserve">・Trả về HTTP 202
 </t>
           </r>
           <r>
@@ -13263,24 +13311,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Sau khi gửi thành công tới toàn bộ địa chỉ,「通知ステータス」được cập nhật thành badge「完了」(`notification_status = 3`, `notified_at` được record)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Do việc gửi email được background worker thực thi bất đồng bộ, nên API trả về HTTP 202 ngay lập tức</t>
+            <t xml:space="preserve">・「通知ステータス」của row JA bị thất bại được hiển thị bằng badge「一部失敗」(`notification_status = 4`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Có thể xác nhận message `一部のJAへの通知メール送信に失敗しました。「通知ステータス」が「一部失敗」の行をご確認ください。`（ACSMS-MSG-023-007）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Chi tiết thất bại được record vào error log (`t_log`, `log_type = 3`)</t>
           </r>
         </is>
       </c>
@@ -13292,7 +13339,7 @@
       <c r="AD52" s="11" t="n"/>
       <c r="AE52" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF52" s="11" t="n"/>
@@ -13334,7 +13381,7 @@
       <c r="BP52" s="10" t="n"/>
       <c r="BQ52" s="11" t="n"/>
     </row>
-    <row r="53" ht="272" customHeight="1">
+    <row r="53" ht="256" customHeight="1">
       <c r="A53" s="44" t="n">
         <v>37</v>
       </c>
@@ -13347,7 +13394,7 @@
       <c r="D53" s="11" t="n"/>
       <c r="E53" s="46" t="inlineStr">
         <is>
-          <t>Gửi email thông báo thất bại tới một phần JA</t>
+          <t>Cancel dialog xác nhận</t>
         </is>
       </c>
       <c r="F53" s="10" t="n"/>
@@ -13357,8 +13404,7 @@
       <c r="J53" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA
-・Chuẩn bị trạng thái trong nhiều JA có 1 JA có địa chỉ email không hợp lệ</t>
+・Đã đăng nhập + đã xác thực MFA</t>
         </is>
       </c>
       <c r="K53" s="10" t="n"/>
@@ -13383,7 +13429,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thực hiện upload nhắm tới nhiều JA (1 JA ở trạng thái gửi thất bại)
+            <t xml:space="preserve">Nhập JA đối tượng, file và ngày dự định xóa rồi click「アップロード実行」
 </t>
           </r>
           <r>
@@ -13400,7 +13446,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Sau khi background worker xử lý, reload màn hình và xác nhận cột「通知ステータス」</t>
+            <t xml:space="preserve">Click「キャンセル」trên dialog xác nhận (ACSMS-MSG-023-008)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận DB: `SELECT COUNT(*) FROM t_file_upload WHERE created_by = :account_id`（so sánh số lượng trước và sau khi click）</t>
           </r>
         </is>
       </c>
@@ -13426,7 +13489,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Trả về HTTP 202
+            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `このファイルをアップロードしますか？`)
 </t>
           </r>
           <r>
@@ -13443,23 +13506,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・「通知ステータス」của row JA bị thất bại được hiển thị bằng badge「一部失敗」(`notification_status = 4`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Có thể xác nhận message `一部のJAへの通知メール送信に失敗しました。「通知ステータス」が「一部失敗」の行をご確認ください。`（ACSMS-MSG-023-007）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Chi tiết thất bại được record vào error log (`t_log`, `log_type = 3`)</t>
+            <t xml:space="preserve">・Màn hình hiện tại được giữ nguyên (nội dung nhập được giữ lại)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Dữ liệu mới không được đăng ký vào `t_file_upload`</t>
           </r>
         </is>
       </c>
@@ -13513,7 +13577,7 @@
       <c r="BP53" s="10" t="n"/>
       <c r="BQ53" s="11" t="n"/>
     </row>
-    <row r="54" ht="256" customHeight="1">
+    <row r="54" ht="160" customHeight="1">
       <c r="A54" s="44" t="n">
         <v>38</v>
       </c>
@@ -13526,7 +13590,7 @@
       <c r="D54" s="11" t="n"/>
       <c r="E54" s="46" t="inlineStr">
         <is>
-          <t>Cancel dialog xác nhận</t>
+          <t>Hủy chọn bằng button clear</t>
         </is>
       </c>
       <c r="F54" s="10" t="n"/>
@@ -13561,7 +13625,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập JA đối tượng, file và ngày dự định xóa rồi click「アップロード実行」
+            <t xml:space="preserve">Click button「クリア」ở trạng thái đã chọn JA đối tượng và file
 </t>
           </r>
           <r>
@@ -13578,24 +13642,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Click「キャンセル」trên dialog xác nhận (ACSMS-MSG-023-008)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận DB: `SELECT COUNT(*) FROM t_file_upload WHERE created_by = :account_id`（so sánh số lượng trước và sau khi click）</t>
+            <t>Click「OK」trên dialog xác nhận</t>
           </r>
         </is>
       </c>
@@ -13621,7 +13668,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `このファイルをアップロードしますか？`)
+            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `全てのJAとファイルを削除します。よろしいでしょうか。`, ACSMS-MSG-023-003)
 </t>
           </r>
           <r>
@@ -13638,24 +13685,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Màn hình hiện tại được giữ nguyên (nội dung nhập được giữ lại)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Dữ liệu mới không được đăng ký vào `t_file_upload`</t>
+            <t>・Danh sách JA đã chọn và danh sách file được clear</t>
           </r>
         </is>
       </c>
@@ -13667,7 +13697,7 @@
       <c r="AD54" s="11" t="n"/>
       <c r="AE54" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF54" s="11" t="n"/>
@@ -13701,7 +13731,12 @@
       <c r="BH54" s="45" t="inlineStr"/>
       <c r="BI54" s="10" t="n"/>
       <c r="BJ54" s="11" t="n"/>
-      <c r="BK54" s="46" t="inlineStr"/>
+      <c r="BK54" s="46" t="inlineStr">
+        <is>
+          <t>Khi chọn「キャンセル」thì không thực hiện xử lý gì.
+---</t>
+        </is>
+      </c>
       <c r="BL54" s="10" t="n"/>
       <c r="BM54" s="10" t="n"/>
       <c r="BN54" s="10" t="n"/>
@@ -13709,166 +13744,74 @@
       <c r="BP54" s="10" t="n"/>
       <c r="BQ54" s="11" t="n"/>
     </row>
-    <row r="55" ht="160" customHeight="1">
-      <c r="A55" s="44" t="n">
-        <v>39</v>
-      </c>
-      <c r="B55" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-039</t>
-        </is>
-      </c>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>Nghiệp vụ — Xóa (Function — Delete)</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="46" t="inlineStr">
-        <is>
-          <t>Hủy chọn bằng button clear</t>
-        </is>
-      </c>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
-      <c r="I55" s="11" t="n"/>
-      <c r="J55" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
-        </is>
-      </c>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="10" t="n"/>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Click button「クリア」ở trạng thái đã chọn JA đối tượng và file
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Click「OK」trên dialog xác nhận</t>
-          </r>
-        </is>
-      </c>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="10" t="n"/>
       <c r="T55" s="10" t="n"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
-      <c r="W55" s="11" t="n"/>
-      <c r="X55" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `全てのJAとファイルを削除します。よろしいでしょうか。`, ACSMS-MSG-023-003)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Danh sách JA đã chọn và danh sách file được clear</t>
-          </r>
-        </is>
-      </c>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
       <c r="Y55" s="10" t="n"/>
       <c r="Z55" s="10" t="n"/>
       <c r="AA55" s="10" t="n"/>
       <c r="AB55" s="10" t="n"/>
       <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="11" t="n"/>
-      <c r="AE55" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF55" s="11" t="n"/>
-      <c r="AG55" s="45" t="inlineStr"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
+      <c r="AF55" s="10" t="n"/>
+      <c r="AG55" s="10" t="n"/>
       <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="11" t="n"/>
-      <c r="AJ55" s="45" t="inlineStr"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
       <c r="AK55" s="10" t="n"/>
-      <c r="AL55" s="11" t="n"/>
-      <c r="AM55" s="45" t="inlineStr"/>
+      <c r="AL55" s="10" t="n"/>
+      <c r="AM55" s="10" t="n"/>
       <c r="AN55" s="10" t="n"/>
-      <c r="AO55" s="11" t="n"/>
-      <c r="AP55" s="45" t="inlineStr"/>
+      <c r="AO55" s="10" t="n"/>
+      <c r="AP55" s="10" t="n"/>
       <c r="AQ55" s="10" t="n"/>
-      <c r="AR55" s="11" t="n"/>
-      <c r="AS55" s="45" t="inlineStr"/>
+      <c r="AR55" s="10" t="n"/>
+      <c r="AS55" s="10" t="n"/>
       <c r="AT55" s="10" t="n"/>
-      <c r="AU55" s="11" t="n"/>
-      <c r="AV55" s="45" t="inlineStr"/>
+      <c r="AU55" s="10" t="n"/>
+      <c r="AV55" s="10" t="n"/>
       <c r="AW55" s="10" t="n"/>
-      <c r="AX55" s="11" t="n"/>
-      <c r="AY55" s="45" t="inlineStr"/>
+      <c r="AX55" s="10" t="n"/>
+      <c r="AY55" s="10" t="n"/>
       <c r="AZ55" s="10" t="n"/>
-      <c r="BA55" s="11" t="n"/>
-      <c r="BB55" s="45" t="inlineStr"/>
+      <c r="BA55" s="10" t="n"/>
+      <c r="BB55" s="10" t="n"/>
       <c r="BC55" s="10" t="n"/>
-      <c r="BD55" s="11" t="n"/>
-      <c r="BE55" s="45" t="inlineStr"/>
+      <c r="BD55" s="10" t="n"/>
+      <c r="BE55" s="10" t="n"/>
       <c r="BF55" s="10" t="n"/>
-      <c r="BG55" s="11" t="n"/>
-      <c r="BH55" s="45" t="inlineStr"/>
+      <c r="BG55" s="10" t="n"/>
+      <c r="BH55" s="10" t="n"/>
       <c r="BI55" s="10" t="n"/>
-      <c r="BJ55" s="11" t="n"/>
-      <c r="BK55" s="46" t="inlineStr">
-        <is>
-          <t>Khi chọn「キャンセル」thì không thực hiện xử lý gì.
----</t>
-        </is>
-      </c>
+      <c r="BJ55" s="10" t="n"/>
+      <c r="BK55" s="10" t="n"/>
       <c r="BL55" s="10" t="n"/>
       <c r="BM55" s="10" t="n"/>
       <c r="BN55" s="10" t="n"/>
@@ -13876,74 +13819,204 @@
       <c r="BP55" s="10" t="n"/>
       <c r="BQ55" s="11" t="n"/>
     </row>
-    <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="32" t="inlineStr">
-        <is>
-          <t>Nghiệp vụ — Download &amp; Xóa (Function — Download &amp; Delete)</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n"/>
+    <row r="56" ht="272" customHeight="1">
+      <c r="A56" s="44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B56" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-039</t>
+        </is>
+      </c>
       <c r="C56" s="10" t="n"/>
-      <c r="D56" s="10" t="n"/>
-      <c r="E56" s="10" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>Xóa file luồng bình thường (xóa logical + xóa vật lý)</t>
+        </is>
+      </c>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
       <c r="H56" s="10" t="n"/>
-      <c r="I56" s="10" t="n"/>
-      <c r="J56" s="10" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA
+・Tồn tại file đối tượng xóa (`deleted_at` là NULL)</t>
+        </is>
+      </c>
       <c r="K56" s="10" t="n"/>
       <c r="L56" s="10" t="n"/>
       <c r="M56" s="10" t="n"/>
       <c r="N56" s="10" t="n"/>
       <c r="O56" s="10" t="n"/>
-      <c r="P56" s="10" t="n"/>
-      <c r="Q56" s="10" t="n"/>
+      <c r="P56" s="11" t="n"/>
+      <c r="Q56" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Click button「削除」của row đối tượng ở「アップロードされたファイルリスト」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Xác định xóa trên dialog xác nhận
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận DB: `SELECT deleted_at FROM t_file_upload WHERE file_upload_id = :id`</t>
+          </r>
+        </is>
+      </c>
       <c r="R56" s="10" t="n"/>
       <c r="S56" s="10" t="n"/>
       <c r="T56" s="10" t="n"/>
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
-      <c r="W56" s="10" t="n"/>
-      <c r="X56" s="10" t="n"/>
+      <c r="W56" s="11" t="n"/>
+      <c r="X56" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `このファイルを削除しますか？`, ACSMS-MSG-023-009)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Dữ liệu bị xóa (message `削除しました。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Bảng được cập nhật, và ngày xóa được hiển thị ở cột「削除日」của row đã xóa
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Bị xóa logical (`deleted_at IS NOT NULL`), và file vật lý bị xóa khỏi storage</t>
+          </r>
+        </is>
+      </c>
       <c r="Y56" s="10" t="n"/>
       <c r="Z56" s="10" t="n"/>
       <c r="AA56" s="10" t="n"/>
       <c r="AB56" s="10" t="n"/>
       <c r="AC56" s="10" t="n"/>
-      <c r="AD56" s="10" t="n"/>
-      <c r="AE56" s="10" t="n"/>
-      <c r="AF56" s="10" t="n"/>
-      <c r="AG56" s="10" t="n"/>
+      <c r="AD56" s="11" t="n"/>
+      <c r="AE56" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF56" s="11" t="n"/>
+      <c r="AG56" s="45" t="inlineStr"/>
       <c r="AH56" s="10" t="n"/>
-      <c r="AI56" s="10" t="n"/>
-      <c r="AJ56" s="10" t="n"/>
+      <c r="AI56" s="11" t="n"/>
+      <c r="AJ56" s="45" t="inlineStr"/>
       <c r="AK56" s="10" t="n"/>
-      <c r="AL56" s="10" t="n"/>
-      <c r="AM56" s="10" t="n"/>
+      <c r="AL56" s="11" t="n"/>
+      <c r="AM56" s="45" t="inlineStr"/>
       <c r="AN56" s="10" t="n"/>
-      <c r="AO56" s="10" t="n"/>
-      <c r="AP56" s="10" t="n"/>
+      <c r="AO56" s="11" t="n"/>
+      <c r="AP56" s="45" t="inlineStr"/>
       <c r="AQ56" s="10" t="n"/>
-      <c r="AR56" s="10" t="n"/>
-      <c r="AS56" s="10" t="n"/>
+      <c r="AR56" s="11" t="n"/>
+      <c r="AS56" s="45" t="inlineStr"/>
       <c r="AT56" s="10" t="n"/>
-      <c r="AU56" s="10" t="n"/>
-      <c r="AV56" s="10" t="n"/>
+      <c r="AU56" s="11" t="n"/>
+      <c r="AV56" s="45" t="inlineStr"/>
       <c r="AW56" s="10" t="n"/>
-      <c r="AX56" s="10" t="n"/>
-      <c r="AY56" s="10" t="n"/>
+      <c r="AX56" s="11" t="n"/>
+      <c r="AY56" s="45" t="inlineStr"/>
       <c r="AZ56" s="10" t="n"/>
-      <c r="BA56" s="10" t="n"/>
-      <c r="BB56" s="10" t="n"/>
+      <c r="BA56" s="11" t="n"/>
+      <c r="BB56" s="45" t="inlineStr"/>
       <c r="BC56" s="10" t="n"/>
-      <c r="BD56" s="10" t="n"/>
-      <c r="BE56" s="10" t="n"/>
+      <c r="BD56" s="11" t="n"/>
+      <c r="BE56" s="45" t="inlineStr"/>
       <c r="BF56" s="10" t="n"/>
-      <c r="BG56" s="10" t="n"/>
-      <c r="BH56" s="10" t="n"/>
+      <c r="BG56" s="11" t="n"/>
+      <c r="BH56" s="45" t="inlineStr"/>
       <c r="BI56" s="10" t="n"/>
-      <c r="BJ56" s="10" t="n"/>
-      <c r="BK56" s="10" t="n"/>
+      <c r="BJ56" s="11" t="n"/>
+      <c r="BK56" s="46" t="inlineStr"/>
       <c r="BL56" s="10" t="n"/>
       <c r="BM56" s="10" t="n"/>
       <c r="BN56" s="10" t="n"/>
@@ -13951,7 +14024,7 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
-    <row r="57" ht="224" customHeight="1">
+    <row r="57" ht="192" customHeight="1">
       <c r="A57" s="44" t="n">
         <v>40</v>
       </c>
@@ -13964,7 +14037,7 @@
       <c r="D57" s="11" t="n"/>
       <c r="E57" s="46" t="inlineStr">
         <is>
-          <t>Download file luồng bình thường</t>
+          <t>Record audit log (xóa)</t>
         </is>
       </c>
       <c r="F57" s="10" t="n"/>
@@ -13975,7 +14048,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã đăng nhập + đã xác thực MFA
-・Tồn tại file đối tượng download (`file_upload_id = 201`)</t>
+・Tồn tại file đối tượng xóa</t>
         </is>
       </c>
       <c r="K57" s="10" t="n"/>
@@ -14000,7 +14073,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thực hiện thao tác download file đối tượng ở「アップロードされたファイルリスト」
+            <t xml:space="preserve">Xóa file
 </t>
           </r>
           <r>
@@ -14017,7 +14090,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận DB: `SELECT download_type FROM t_file_download ORDER BY created_at DESC LIMIT 1` và `SELECT operation FROM t_log WHERE target_table = 't_file_upload' AND operation = 'DOWNLOAD' ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t>Xác nhận DB: `SELECT log_type, operation, result_status, before_value FROM t_log WHERE target_table = 't_file_upload' AND operation = 'DELETE' ORDER BY log_datetime DESC LIMIT 1`</t>
           </r>
         </is>
       </c>
@@ -14043,7 +14116,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Trả về HTTP 200 (Content-Disposition: `attachment; filename="..."`, binary của file được download)
+            <t xml:space="preserve">・Dữ liệu bị xóa (message `削除しました。`)
 </t>
           </r>
           <r>
@@ -14060,15 +14133,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Lịch sử download được record vào `t_file_download` (`download_type = 2`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Audit log được record (`operation = 'DOWNLOAD'`, `log_type = 4`)</t>
+            <t xml:space="preserve">・Audit log được record (`log_type = 4`, `operation = 'DELETE'`, `result_status = 1`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Dữ liệu trước khi xóa được record dưới dạng JSON ở `before_value`</t>
           </r>
         </is>
       </c>
@@ -14122,7 +14195,7 @@
       <c r="BP57" s="10" t="n"/>
       <c r="BQ57" s="11" t="n"/>
     </row>
-    <row r="58" ht="272" customHeight="1">
+    <row r="58" ht="112" customHeight="1">
       <c r="A58" s="44" t="n">
         <v>41</v>
       </c>
@@ -14135,7 +14208,7 @@
       <c r="D58" s="11" t="n"/>
       <c r="E58" s="46" t="inlineStr">
         <is>
-          <t>Xóa file luồng bình thường (xóa logical + xóa vật lý)</t>
+          <t>Điều khiển active／disable của button xóa</t>
         </is>
       </c>
       <c r="F58" s="10" t="n"/>
@@ -14146,7 +14219,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã đăng nhập + đã xác thực MFA
-・Tồn tại file đối tượng xóa (`deleted_at` là NULL)</t>
+・Tồn tại từ 1 row trở lên cho mỗi loại: row có `deleted_at` NULL và row có `deleted_at` NOT NULL</t>
         </is>
       </c>
       <c r="K58" s="10" t="n"/>
@@ -14171,41 +14244,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Click button「削除」của row đối tượng ở「アップロードされたファイルリスト」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Xác định xóa trên dialog xác nhận
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận DB: `SELECT deleted_at FROM t_file_upload WHERE file_upload_id = :id`</t>
+            <t>Xác nhận trạng thái của button「削除」từng row ở「アップロードされたファイルリスト」</t>
           </r>
         </is>
       </c>
@@ -14231,49 +14270,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `このファイルを削除しますか？`, ACSMS-MSG-023-009)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Dữ liệu bị xóa (message `削除しました。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Bảng được cập nhật, và ngày xóa được hiển thị ở cột「削除日」của row đã xóa
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Bị xóa logical (`deleted_at IS NOT NULL`), và file vật lý bị xóa khỏi storage</t>
+            <t xml:space="preserve">・Row có `deleted_at` NULL thì button「削除」được hiển thị ở trạng thái active
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Row có `deleted_at` NOT NULL thì button「削除」được hiển thị ở trạng thái disable</t>
           </r>
         </is>
       </c>
@@ -14327,7 +14332,7 @@
       <c r="BP58" s="10" t="n"/>
       <c r="BQ58" s="11" t="n"/>
     </row>
-    <row r="59" ht="192" customHeight="1">
+    <row r="59" ht="208" customHeight="1">
       <c r="A59" s="44" t="n">
         <v>42</v>
       </c>
@@ -14340,7 +14345,7 @@
       <c r="D59" s="11" t="n"/>
       <c r="E59" s="46" t="inlineStr">
         <is>
-          <t>Record audit log (xóa)</t>
+          <t>Cancel dialog xác nhận xóa</t>
         </is>
       </c>
       <c r="F59" s="10" t="n"/>
@@ -14351,7 +14356,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã đăng nhập + đã xác thực MFA
-・Tồn tại file đối tượng xóa</t>
+・Tồn tại file đối tượng xóa (`deleted_at` là NULL)</t>
         </is>
       </c>
       <c r="K59" s="10" t="n"/>
@@ -14376,7 +14381,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xóa file
+            <t xml:space="preserve">Click button「削除」của row đối tượng
 </t>
           </r>
           <r>
@@ -14393,7 +14398,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận DB: `SELECT log_type, operation, result_status, before_value FROM t_log WHERE target_table = 't_file_upload' AND operation = 'DELETE' ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t xml:space="preserve">Click「キャンセル」trên dialog xác nhận (ACSMS-MSG-023-009)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận DB: `SELECT deleted_at FROM t_file_upload WHERE file_upload_id = :id`</t>
           </r>
         </is>
       </c>
@@ -14419,7 +14441,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Dữ liệu bị xóa (message `削除しました。`)
+            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `このファイルを削除しますか？`)
 </t>
           </r>
           <r>
@@ -14436,15 +14458,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Audit log được record (`log_type = 4`, `operation = 'DELETE'`, `result_status = 1`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Dữ liệu trước khi xóa được record dưới dạng JSON ở `before_value`</t>
+            <t xml:space="preserve">・Màn hình hiện tại được giữ nguyên
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Dữ liệu không bị xóa (vẫn ở `deleted_at IS NULL`)</t>
           </r>
         </is>
       </c>
@@ -14456,7 +14487,7 @@
       <c r="AD59" s="11" t="n"/>
       <c r="AE59" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF59" s="11" t="n"/>
@@ -14498,136 +14529,74 @@
       <c r="BP59" s="10" t="n"/>
       <c r="BQ59" s="11" t="n"/>
     </row>
-    <row r="60" ht="112" customHeight="1">
-      <c r="A60" s="44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B60" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-043</t>
-        </is>
-      </c>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>Xử lý lỗi chung (Common Error Handling)</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
-      <c r="D60" s="11" t="n"/>
-      <c r="E60" s="46" t="inlineStr">
-        <is>
-          <t>Điều khiển active／disable của button xóa</t>
-        </is>
-      </c>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="11" t="n"/>
-      <c r="J60" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA
-・Tồn tại từ 1 row trở lên cho mỗi loại: row có `deleted_at` NULL và row có `deleted_at` NOT NULL</t>
-        </is>
-      </c>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
       <c r="K60" s="10" t="n"/>
       <c r="L60" s="10" t="n"/>
       <c r="M60" s="10" t="n"/>
       <c r="N60" s="10" t="n"/>
       <c r="O60" s="10" t="n"/>
-      <c r="P60" s="11" t="n"/>
-      <c r="Q60" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận trạng thái của button「削除」từng row ở「アップロードされたファイルリスト」</t>
-          </r>
-        </is>
-      </c>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
       <c r="R60" s="10" t="n"/>
       <c r="S60" s="10" t="n"/>
       <c r="T60" s="10" t="n"/>
       <c r="U60" s="10" t="n"/>
       <c r="V60" s="10" t="n"/>
-      <c r="W60" s="11" t="n"/>
-      <c r="X60" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Row có `deleted_at` NULL thì button「削除」được hiển thị ở trạng thái active
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Row có `deleted_at` NOT NULL thì button「削除」được hiển thị ở trạng thái disable</t>
-          </r>
-        </is>
-      </c>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
       <c r="Y60" s="10" t="n"/>
       <c r="Z60" s="10" t="n"/>
       <c r="AA60" s="10" t="n"/>
       <c r="AB60" s="10" t="n"/>
       <c r="AC60" s="10" t="n"/>
-      <c r="AD60" s="11" t="n"/>
-      <c r="AE60" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF60" s="11" t="n"/>
-      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
       <c r="AH60" s="10" t="n"/>
-      <c r="AI60" s="11" t="n"/>
-      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
       <c r="AK60" s="10" t="n"/>
-      <c r="AL60" s="11" t="n"/>
-      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AL60" s="10" t="n"/>
+      <c r="AM60" s="10" t="n"/>
       <c r="AN60" s="10" t="n"/>
-      <c r="AO60" s="11" t="n"/>
-      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AO60" s="10" t="n"/>
+      <c r="AP60" s="10" t="n"/>
       <c r="AQ60" s="10" t="n"/>
-      <c r="AR60" s="11" t="n"/>
-      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AR60" s="10" t="n"/>
+      <c r="AS60" s="10" t="n"/>
       <c r="AT60" s="10" t="n"/>
-      <c r="AU60" s="11" t="n"/>
-      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AU60" s="10" t="n"/>
+      <c r="AV60" s="10" t="n"/>
       <c r="AW60" s="10" t="n"/>
-      <c r="AX60" s="11" t="n"/>
-      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AX60" s="10" t="n"/>
+      <c r="AY60" s="10" t="n"/>
       <c r="AZ60" s="10" t="n"/>
-      <c r="BA60" s="11" t="n"/>
-      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BA60" s="10" t="n"/>
+      <c r="BB60" s="10" t="n"/>
       <c r="BC60" s="10" t="n"/>
-      <c r="BD60" s="11" t="n"/>
-      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BD60" s="10" t="n"/>
+      <c r="BE60" s="10" t="n"/>
       <c r="BF60" s="10" t="n"/>
-      <c r="BG60" s="11" t="n"/>
-      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BG60" s="10" t="n"/>
+      <c r="BH60" s="10" t="n"/>
       <c r="BI60" s="10" t="n"/>
-      <c r="BJ60" s="11" t="n"/>
-      <c r="BK60" s="46" t="inlineStr"/>
+      <c r="BJ60" s="10" t="n"/>
+      <c r="BK60" s="10" t="n"/>
       <c r="BL60" s="10" t="n"/>
       <c r="BM60" s="10" t="n"/>
       <c r="BN60" s="10" t="n"/>
@@ -14635,20 +14604,20 @@
       <c r="BP60" s="10" t="n"/>
       <c r="BQ60" s="11" t="n"/>
     </row>
-    <row r="61" ht="208" customHeight="1">
+    <row r="61" ht="128" customHeight="1">
       <c r="A61" s="44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B61" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-023-044</t>
+          <t>ACSMS-TC-023-043</t>
         </is>
       </c>
       <c r="C61" s="10" t="n"/>
       <c r="D61" s="11" t="n"/>
       <c r="E61" s="46" t="inlineStr">
         <is>
-          <t>Cancel dialog xác nhận xóa</t>
+          <t>Xử lý 401 khi session hết hạn</t>
         </is>
       </c>
       <c r="F61" s="10" t="n"/>
@@ -14659,7 +14628,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã đăng nhập + đã xác thực MFA
-・Tồn tại file đối tượng xóa (`deleted_at` là NULL)</t>
+・Trạng thái session đã bị làm hết hạn cưỡng chế</t>
         </is>
       </c>
       <c r="K61" s="10" t="n"/>
@@ -14684,41 +14653,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Click button「削除」của row đối tượng
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Click「キャンセル」trên dialog xác nhận (ACSMS-MSG-023-009)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận DB: `SELECT deleted_at FROM t_file_upload WHERE file_upload_id = :id`</t>
+            <t>Sau khi session hết hạn, thực hiện thao tác bất kỳ trên màn hình (fetch lại danh sách file v.v.)</t>
           </r>
         </is>
       </c>
@@ -14744,41 +14679,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Dialog xác nhận được hiển thị (message `このファイルを削除しますか？`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Màn hình hiện tại được giữ nguyên
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Dữ liệu không bị xóa (vẫn ở `deleted_at IS NULL`)</t>
+            <t xml:space="preserve">・Trả về HTTP 401 (`error_code: UNAUTHORIZED`, message `セッションが切れました。再度ログインしてください。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Khi session hết hạn, chuyển sang màn hình đăng nhập (`/login?redirect=...`)</t>
           </r>
         </is>
       </c>
@@ -14832,20 +14741,20 @@
       <c r="BP61" s="10" t="n"/>
       <c r="BQ61" s="11" t="n"/>
     </row>
-    <row r="62" ht="176" customHeight="1">
+    <row r="62" ht="80" customHeight="1">
       <c r="A62" s="44" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-023-045</t>
+          <t>ACSMS-TC-023-044</t>
         </is>
       </c>
       <c r="C62" s="10" t="n"/>
       <c r="D62" s="11" t="n"/>
       <c r="E62" s="46" t="inlineStr">
         <is>
-          <t>Download file đã xóa (NOT_FOUND)</t>
+          <t>Gửi request parameter không hợp lệ (BAD_REQUEST)</t>
         </is>
       </c>
       <c r="F62" s="10" t="n"/>
@@ -14855,8 +14764,7 @@
       <c r="J62" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA
-・Tồn tại file đã xóa logical (`deleted_at IS NOT NULL`) (`file_upload_id = 301`)</t>
+・Đã đăng nhập + đã xác thực MFA</t>
         </is>
       </c>
       <c r="K62" s="10" t="n"/>
@@ -14881,7 +14789,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gửi trực tiếp GET `/api/v1/file-upload/301/download` bằng DevTools</t>
+            <t>Gửi query parameter không hợp lệ như GET `/api/v1/file-upload?status=abc&amp;page=-1` bằng DevTools</t>
           </r>
         </is>
       </c>
@@ -14907,24 +14815,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 404 (`error_code: NOT_FOUND`, message `指定されたファイルが見つかりません。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Record đã xóa logical không phải là đối tượng download (bị loại trừ bằng điều kiện `deleted_at IS NULL`)</t>
+            <t>Trả về HTTP 400 (`error_code: BAD_REQUEST`, message `リクエストパラメータが不正です。`)</t>
           </r>
         </is>
       </c>
@@ -14970,12 +14861,7 @@
       <c r="BH62" s="45" t="inlineStr"/>
       <c r="BI62" s="10" t="n"/>
       <c r="BJ62" s="11" t="n"/>
-      <c r="BK62" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK62" s="46" t="inlineStr"/>
       <c r="BL62" s="10" t="n"/>
       <c r="BM62" s="10" t="n"/>
       <c r="BN62" s="10" t="n"/>
@@ -14983,74 +14869,135 @@
       <c r="BP62" s="10" t="n"/>
       <c r="BQ62" s="11" t="n"/>
     </row>
-    <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="32" t="inlineStr">
-        <is>
-          <t>Xử lý lỗi chung (Common Error Handling)</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="n"/>
+    <row r="63" ht="176" customHeight="1">
+      <c r="A63" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-045</t>
+        </is>
+      </c>
       <c r="C63" s="10" t="n"/>
-      <c r="D63" s="10" t="n"/>
-      <c r="E63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>Lỗi validation (hình dạng mảng errors)</t>
+        </is>
+      </c>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n"/>
-      <c r="I63" s="10" t="n"/>
-      <c r="J63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA</t>
+        </is>
+      </c>
       <c r="K63" s="10" t="n"/>
       <c r="L63" s="10" t="n"/>
       <c r="M63" s="10" t="n"/>
       <c r="N63" s="10" t="n"/>
       <c r="O63" s="10" t="n"/>
-      <c r="P63" s="10" t="n"/>
-      <c r="Q63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Gửi POST `/api/v1/file-upload` ở trạng thái chưa chỉ định JA đối tượng (`ja_ids` trống) bằng DevTools</t>
+          </r>
+        </is>
+      </c>
       <c r="R63" s="10" t="n"/>
       <c r="S63" s="10" t="n"/>
       <c r="T63" s="10" t="n"/>
       <c r="U63" s="10" t="n"/>
       <c r="V63" s="10" t="n"/>
-      <c r="W63" s="10" t="n"/>
-      <c r="X63" s="10" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP 400 (`error_code: VALIDATION_ERROR`, message `入力値が不正です。詳細はerrorsフィールドを確認してください。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Response chứa mảng `errors`, có hình dạng `{ field, message }` (ví dụ: `field: "ja_ids"`, `message: "対象JAを1つ以上選択してください。"`)</t>
+          </r>
+        </is>
+      </c>
       <c r="Y63" s="10" t="n"/>
       <c r="Z63" s="10" t="n"/>
       <c r="AA63" s="10" t="n"/>
       <c r="AB63" s="10" t="n"/>
       <c r="AC63" s="10" t="n"/>
-      <c r="AD63" s="10" t="n"/>
-      <c r="AE63" s="10" t="n"/>
-      <c r="AF63" s="10" t="n"/>
-      <c r="AG63" s="10" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF63" s="11" t="n"/>
+      <c r="AG63" s="45" t="inlineStr"/>
       <c r="AH63" s="10" t="n"/>
-      <c r="AI63" s="10" t="n"/>
-      <c r="AJ63" s="10" t="n"/>
+      <c r="AI63" s="11" t="n"/>
+      <c r="AJ63" s="45" t="inlineStr"/>
       <c r="AK63" s="10" t="n"/>
-      <c r="AL63" s="10" t="n"/>
-      <c r="AM63" s="10" t="n"/>
+      <c r="AL63" s="11" t="n"/>
+      <c r="AM63" s="45" t="inlineStr"/>
       <c r="AN63" s="10" t="n"/>
-      <c r="AO63" s="10" t="n"/>
-      <c r="AP63" s="10" t="n"/>
+      <c r="AO63" s="11" t="n"/>
+      <c r="AP63" s="45" t="inlineStr"/>
       <c r="AQ63" s="10" t="n"/>
-      <c r="AR63" s="10" t="n"/>
-      <c r="AS63" s="10" t="n"/>
+      <c r="AR63" s="11" t="n"/>
+      <c r="AS63" s="45" t="inlineStr"/>
       <c r="AT63" s="10" t="n"/>
-      <c r="AU63" s="10" t="n"/>
-      <c r="AV63" s="10" t="n"/>
+      <c r="AU63" s="11" t="n"/>
+      <c r="AV63" s="45" t="inlineStr"/>
       <c r="AW63" s="10" t="n"/>
-      <c r="AX63" s="10" t="n"/>
-      <c r="AY63" s="10" t="n"/>
+      <c r="AX63" s="11" t="n"/>
+      <c r="AY63" s="45" t="inlineStr"/>
       <c r="AZ63" s="10" t="n"/>
-      <c r="BA63" s="10" t="n"/>
-      <c r="BB63" s="10" t="n"/>
+      <c r="BA63" s="11" t="n"/>
+      <c r="BB63" s="45" t="inlineStr"/>
       <c r="BC63" s="10" t="n"/>
-      <c r="BD63" s="10" t="n"/>
-      <c r="BE63" s="10" t="n"/>
+      <c r="BD63" s="11" t="n"/>
+      <c r="BE63" s="45" t="inlineStr"/>
       <c r="BF63" s="10" t="n"/>
-      <c r="BG63" s="10" t="n"/>
-      <c r="BH63" s="10" t="n"/>
+      <c r="BG63" s="11" t="n"/>
+      <c r="BH63" s="45" t="inlineStr"/>
       <c r="BI63" s="10" t="n"/>
-      <c r="BJ63" s="10" t="n"/>
-      <c r="BK63" s="10" t="n"/>
+      <c r="BJ63" s="11" t="n"/>
+      <c r="BK63" s="46" t="inlineStr"/>
       <c r="BL63" s="10" t="n"/>
       <c r="BM63" s="10" t="n"/>
       <c r="BN63" s="10" t="n"/>
@@ -15058,7 +15005,7 @@
       <c r="BP63" s="10" t="n"/>
       <c r="BQ63" s="11" t="n"/>
     </row>
-    <row r="64" ht="128" customHeight="1">
+    <row r="64" ht="96" customHeight="1">
       <c r="A64" s="44" t="n">
         <v>46</v>
       </c>
@@ -15071,7 +15018,7 @@
       <c r="D64" s="11" t="n"/>
       <c r="E64" s="46" t="inlineStr">
         <is>
-          <t>Xử lý 401 khi session hết hạn</t>
+          <t>Vượt quá rate limit (TOO_MANY_REQUESTS)</t>
         </is>
       </c>
       <c r="F64" s="10" t="n"/>
@@ -15081,8 +15028,7 @@
       <c r="J64" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA
-・Trạng thái session đã bị làm hết hạn cưỡng chế</t>
+・Đã đăng nhập + đã xác thực MFA</t>
         </is>
       </c>
       <c r="K64" s="10" t="n"/>
@@ -15107,7 +15053,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Sau khi session hết hạn, thực hiện thao tác bất kỳ trên màn hình (fetch lại danh sách file v.v.)</t>
+            <t>Gửi liên tục số lần request vượt quá giới hạn trong thời gian ngắn</t>
           </r>
         </is>
       </c>
@@ -15133,15 +15079,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Trả về HTTP 401 (`error_code: UNAUTHORIZED`, message `セッションが切れました。再度ログインしてください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Khi session hết hạn, chuyển sang màn hình đăng nhập (`/login?redirect=...`)</t>
+            <t>Trả về HTTP 429 (`error_code: TOO_MANY_REQUESTS`, message `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`)</t>
           </r>
         </is>
       </c>
@@ -15195,7 +15133,7 @@
       <c r="BP64" s="10" t="n"/>
       <c r="BQ64" s="11" t="n"/>
     </row>
-    <row r="65" ht="80" customHeight="1">
+    <row r="65" ht="304" customHeight="1">
       <c r="A65" s="44" t="n">
         <v>47</v>
       </c>
@@ -15208,7 +15146,7 @@
       <c r="D65" s="11" t="n"/>
       <c r="E65" s="46" t="inlineStr">
         <is>
-          <t>Gửi request parameter không hợp lệ (BAD_REQUEST)</t>
+          <t>Lỗi server (INTERNAL_SERVER_ERROR)</t>
         </is>
       </c>
       <c r="F65" s="10" t="n"/>
@@ -15218,7 +15156,8 @@
       <c r="J65" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
+・Đã đăng nhập + đã xác thực MFA
+・Trạng thái có thể giả lập ghi storage thất bại</t>
         </is>
       </c>
       <c r="K65" s="10" t="n"/>
@@ -15243,7 +15182,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gửi query parameter không hợp lệ như GET `/api/v1/file-upload?status=abc&amp;page=-1` bằng DevTools</t>
+            <t xml:space="preserve">Thực hiện upload ở trạng thái giả lập ghi storage thất bại
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận DB: `SELECT COUNT(*) FROM t_file_upload WHERE created_by = :account_id`（so sánh số lượng trước và sau khi thực hiện）</t>
           </r>
         </is>
       </c>
@@ -15269,7 +15225,40 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Trả về HTTP 400 (`error_code: BAD_REQUEST`, message `リクエストパラメータが不正です。`)</t>
+            <t xml:space="preserve">Trả về HTTP 500 (`error_code: INTERNAL_SERVER_ERROR`, message `システムエラーが発生しました。しばらくしてから再度お試しください。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Message upload thất bại `アップロードに失敗しました。しばらくしてから再度お試しください。`（ACSMS-MSG-023-005）được hiển thị trên màn hình
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Transaction được rollback, và dữ liệu mới không được đăng ký vào `t_file_upload`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・File vật lý đã được lưu được xóa bù trừ (compensating delete)</t>
           </r>
         </is>
       </c>
@@ -15323,7 +15312,7 @@
       <c r="BP65" s="10" t="n"/>
       <c r="BQ65" s="11" t="n"/>
     </row>
-    <row r="66" ht="176" customHeight="1">
+    <row r="66" ht="80" customHeight="1">
       <c r="A66" s="44" t="n">
         <v>48</v>
       </c>
@@ -15336,7 +15325,7 @@
       <c r="D66" s="11" t="n"/>
       <c r="E66" s="46" t="inlineStr">
         <is>
-          <t>Lỗi validation (hình dạng mảng errors)</t>
+          <t>Lấy resource đã xóa (NOT_FOUND)</t>
         </is>
       </c>
       <c r="F66" s="10" t="n"/>
@@ -15346,7 +15335,8 @@
       <c r="J66" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
+・Đã đăng nhập + đã xác thực MFA
+・Tồn tại file đã xóa logical (`file_upload_id = 301`)</t>
         </is>
       </c>
       <c r="K66" s="10" t="n"/>
@@ -15371,7 +15361,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gửi POST `/api/v1/file-upload` ở trạng thái chưa chỉ định JA đối tượng (`ja_ids` trống) bằng DevTools</t>
+            <t>Gửi trực tiếp DELETE `/api/v1/file-upload/301` bằng DevTools (record đã bị xóa)</t>
           </r>
         </is>
       </c>
@@ -15397,15 +15387,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 400 (`error_code: VALIDATION_ERROR`, message `入力値が不正です。詳細はerrorsフィールドを確認してください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Response chứa mảng `errors`, có hình dạng `{ field, message }` (ví dụ: `field: "ja_ids"`, `message: "対象JAを1つ以上選択してください。"`)</t>
+            <t>Trả về HTTP 404 (`error_code: NOT_FOUND`, message `指定されたファイルが見つかりません。`)</t>
           </r>
         </is>
       </c>
@@ -15472,7 +15454,7 @@
       <c r="D67" s="11" t="n"/>
       <c r="E67" s="46" t="inlineStr">
         <is>
-          <t>Vượt quá rate limit (TOO_MANY_REQUESTS)</t>
+          <t>Xử lý khi mất kết nối mạng</t>
         </is>
       </c>
       <c r="F67" s="10" t="n"/>
@@ -15507,7 +15489,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gửi liên tục số lần request vượt quá giới hạn trong thời gian ngắn</t>
+            <t>Click「アップロード実行」ở trạng thái giả lập mất kết nối mạng ở tab Network của DevTools</t>
           </r>
         </is>
       </c>
@@ -15533,7 +15515,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Trả về HTTP 429 (`error_code: TOO_MANY_REQUESTS`, message `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`)</t>
+            <t xml:space="preserve">・Toast lỗi mạng được hiển thị ở phía frontend
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Không phát sinh lỗi ngoài dự kiến (màn hình không bị terminate bất thường)</t>
           </r>
         </is>
       </c>
@@ -15587,178 +15577,74 @@
       <c r="BP67" s="10" t="n"/>
       <c r="BQ67" s="11" t="n"/>
     </row>
-    <row r="68" ht="304" customHeight="1">
-      <c r="A68" s="44" t="n">
-        <v>50</v>
-      </c>
-      <c r="B68" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-023-050</t>
-        </is>
-      </c>
+    <row r="68" ht="22.5" customHeight="1">
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>Business logic — Liên kết・Preview・Download (Function — Link / Preview / Download)</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n"/>
       <c r="C68" s="10" t="n"/>
-      <c r="D68" s="11" t="n"/>
-      <c r="E68" s="46" t="inlineStr">
-        <is>
-          <t>Lỗi server (INTERNAL_SERVER_ERROR)</t>
-        </is>
-      </c>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="10" t="n"/>
       <c r="H68" s="10" t="n"/>
-      <c r="I68" s="11" t="n"/>
-      <c r="J68" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA
-・Trạng thái có thể giả lập ghi storage thất bại</t>
-        </is>
-      </c>
+      <c r="I68" s="10" t="n"/>
+      <c r="J68" s="10" t="n"/>
       <c r="K68" s="10" t="n"/>
       <c r="L68" s="10" t="n"/>
       <c r="M68" s="10" t="n"/>
       <c r="N68" s="10" t="n"/>
       <c r="O68" s="10" t="n"/>
-      <c r="P68" s="11" t="n"/>
-      <c r="Q68" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Thực hiện upload ở trạng thái giả lập ghi storage thất bại
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận DB: `SELECT COUNT(*) FROM t_file_upload WHERE created_by = :account_id`（so sánh số lượng trước và sau khi thực hiện）</t>
-          </r>
-        </is>
-      </c>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
       <c r="R68" s="10" t="n"/>
       <c r="S68" s="10" t="n"/>
       <c r="T68" s="10" t="n"/>
       <c r="U68" s="10" t="n"/>
       <c r="V68" s="10" t="n"/>
-      <c r="W68" s="11" t="n"/>
-      <c r="X68" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Trả về HTTP 500 (`error_code: INTERNAL_SERVER_ERROR`, message `システムエラーが発生しました。しばらくしてから再度お試しください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Message upload thất bại `アップロードに失敗しました。しばらくしてから再度お試しください。`（ACSMS-MSG-023-005）được hiển thị trên màn hình
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Transaction được rollback, và dữ liệu mới không được đăng ký vào `t_file_upload`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・File vật lý đã được lưu được xóa bù trừ (compensating delete)</t>
-          </r>
-        </is>
-      </c>
+      <c r="W68" s="10" t="n"/>
+      <c r="X68" s="10" t="n"/>
       <c r="Y68" s="10" t="n"/>
       <c r="Z68" s="10" t="n"/>
       <c r="AA68" s="10" t="n"/>
       <c r="AB68" s="10" t="n"/>
       <c r="AC68" s="10" t="n"/>
-      <c r="AD68" s="11" t="n"/>
-      <c r="AE68" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF68" s="11" t="n"/>
-      <c r="AG68" s="45" t="inlineStr"/>
+      <c r="AD68" s="10" t="n"/>
+      <c r="AE68" s="10" t="n"/>
+      <c r="AF68" s="10" t="n"/>
+      <c r="AG68" s="10" t="n"/>
       <c r="AH68" s="10" t="n"/>
-      <c r="AI68" s="11" t="n"/>
-      <c r="AJ68" s="45" t="inlineStr"/>
+      <c r="AI68" s="10" t="n"/>
+      <c r="AJ68" s="10" t="n"/>
       <c r="AK68" s="10" t="n"/>
-      <c r="AL68" s="11" t="n"/>
-      <c r="AM68" s="45" t="inlineStr"/>
+      <c r="AL68" s="10" t="n"/>
+      <c r="AM68" s="10" t="n"/>
       <c r="AN68" s="10" t="n"/>
-      <c r="AO68" s="11" t="n"/>
-      <c r="AP68" s="45" t="inlineStr"/>
+      <c r="AO68" s="10" t="n"/>
+      <c r="AP68" s="10" t="n"/>
       <c r="AQ68" s="10" t="n"/>
-      <c r="AR68" s="11" t="n"/>
-      <c r="AS68" s="45" t="inlineStr"/>
+      <c r="AR68" s="10" t="n"/>
+      <c r="AS68" s="10" t="n"/>
       <c r="AT68" s="10" t="n"/>
-      <c r="AU68" s="11" t="n"/>
-      <c r="AV68" s="45" t="inlineStr"/>
+      <c r="AU68" s="10" t="n"/>
+      <c r="AV68" s="10" t="n"/>
       <c r="AW68" s="10" t="n"/>
-      <c r="AX68" s="11" t="n"/>
-      <c r="AY68" s="45" t="inlineStr"/>
+      <c r="AX68" s="10" t="n"/>
+      <c r="AY68" s="10" t="n"/>
       <c r="AZ68" s="10" t="n"/>
-      <c r="BA68" s="11" t="n"/>
-      <c r="BB68" s="45" t="inlineStr"/>
+      <c r="BA68" s="10" t="n"/>
+      <c r="BB68" s="10" t="n"/>
       <c r="BC68" s="10" t="n"/>
-      <c r="BD68" s="11" t="n"/>
-      <c r="BE68" s="45" t="inlineStr"/>
+      <c r="BD68" s="10" t="n"/>
+      <c r="BE68" s="10" t="n"/>
       <c r="BF68" s="10" t="n"/>
-      <c r="BG68" s="11" t="n"/>
-      <c r="BH68" s="45" t="inlineStr"/>
+      <c r="BG68" s="10" t="n"/>
+      <c r="BH68" s="10" t="n"/>
       <c r="BI68" s="10" t="n"/>
-      <c r="BJ68" s="11" t="n"/>
-      <c r="BK68" s="46" t="inlineStr"/>
+      <c r="BJ68" s="10" t="n"/>
+      <c r="BK68" s="10" t="n"/>
       <c r="BL68" s="10" t="n"/>
       <c r="BM68" s="10" t="n"/>
       <c r="BN68" s="10" t="n"/>
@@ -15766,20 +15652,20 @@
       <c r="BP68" s="10" t="n"/>
       <c r="BQ68" s="11" t="n"/>
     </row>
-    <row r="69" ht="80" customHeight="1">
+    <row r="69" ht="450" customHeight="1">
       <c r="A69" s="44" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B69" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-023-051</t>
+          <t>ACSMS-TC-023-050</t>
         </is>
       </c>
       <c r="C69" s="10" t="n"/>
       <c r="D69" s="11" t="n"/>
       <c r="E69" s="46" t="inlineStr">
         <is>
-          <t>Lấy resource đã xóa (NOT_FOUND)</t>
+          <t>File đã upload lấy được từ màn hình download (SCR-022)</t>
         </is>
       </c>
       <c r="F69" s="10" t="n"/>
@@ -15788,9 +15674,9 @@
       <c r="I69" s="11" t="n"/>
       <c r="J69" s="46" t="inlineStr">
         <is>
-          <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA
-・Tồn tại file đã xóa logical (`file_upload_id = 301`)</t>
+          <t>・Đăng nhập bằng role NICHINO_STAFF (có quyền `file.upload`)
+・Tồn tại JA「JA北海道」(ja_id=100), JA đó có tài khoản JA_HONTEN (role 4) với quyền `file.download`
+・JA khác「JA東京」(ja_id=200) cũng có tài khoản JA_HONTEN (dùng để kiểm tra scope)</t>
         </is>
       </c>
       <c r="K69" s="10" t="n"/>
@@ -15815,7 +15701,75 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gửi trực tiếp DELETE `/api/v1/file-upload/301` bằng DevTools (record đã bị xóa)</t>
+            <t xml:space="preserve">Tại màn hình upload file, chọn JA đối tượng chỉ「JA北海道」, ngày dự định xóa là ngày 1 tháng sau, upload 1 file `検査結果.xlsx`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra dòng tương ứng của `t_file_upload` và `t_file_download` trên DB
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Đăng nhập bằng tài khoản JA_HONTEN của「JA北海道」, mở màn hình download file, tìm theo tên file rồi bấm link tên file
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Đăng nhập bằng tài khoản JA_HONTEN của「JA東京」, tìm cùng tên file đó ở màn hình download file
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Quay lại màn hình upload bằng tài khoản đã upload (NICHINO_STAFF), thực hiện「削除」dòng đó rồi mở lại màn hình download file</t>
           </r>
         </is>
       </c>
@@ -15841,7 +15795,108 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Trả về HTTP 404 (`error_code: NOT_FOUND`, message `指定されたファイルが見つかりません。`)</t>
+            <t xml:space="preserve">Trả về HTTP 202 và hiển thị ACSMS-MSG-023-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Ứng với 1 dòng `t_file_upload` cũng có 1 dòng được đăng ký vào `t_file_download`, với `ja_id`=100, `download_type`=2 (khác), `nichino_download_allowed_flg`=TRUE, `record_count`=0, `file_path` trùng khớp
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">File tương ứng hiển thị trong danh sách, download thành công và nội dung khớp với file đã đưa vào
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">0 bản ghi (theo DataScope thì không thấy file của JA khác)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">File tương ứng biến mất khỏi danh sách của màn hình download (`t_file_download.deleted_at` cũng được thiết lập). Không được rơi vào trạng thái thực thể (S3) đã mất nhưng vẫn còn trong danh sách
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Màn hình download chỉ lấy `t_file_download` làm đối tượng danh sách・truy xuất, nên nếu lúc upload không đăng ký dòng cặp thì phía JA (role 3/4/5) hoàn toàn không lấy được file (yêu cầu khách hàng 2026-08)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Cố định `nichino_download_allowed_flg`=TRUE là vì nếu Nichino・trung ương hội không lấy lại được file do chính tổ chức mình đưa lên thì vận hành không chạy được. Các màn xuất báo biểu (SCR-021/026/028/029) thì cố định／chọn theo từng màn; đây là mặc định riêng của màn này
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Khóa đối chiếu của dòng cặp là `file_path`. Do khóa S3 có chứa UUID nên là duy nhất, giải quyết được cặp mà không cần thêm cột FK (kèm migration + ảnh hưởng tới các dòng báo biểu hiện có)</t>
           </r>
         </is>
       </c>
@@ -15853,7 +15908,7 @@
       <c r="AD69" s="11" t="n"/>
       <c r="AE69" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF69" s="11" t="n"/>
@@ -15887,7 +15942,12 @@
       <c r="BH69" s="45" t="inlineStr"/>
       <c r="BI69" s="10" t="n"/>
       <c r="BJ69" s="11" t="n"/>
-      <c r="BK69" s="46" t="inlineStr"/>
+      <c r="BK69" s="46" t="inlineStr">
+        <is>
+          <t>(không có)
+---</t>
+        </is>
+      </c>
       <c r="BL69" s="10" t="n"/>
       <c r="BM69" s="10" t="n"/>
       <c r="BN69" s="10" t="n"/>
@@ -15895,20 +15955,20 @@
       <c r="BP69" s="10" t="n"/>
       <c r="BQ69" s="11" t="n"/>
     </row>
-    <row r="70" ht="96" customHeight="1">
+    <row r="70" ht="450" customHeight="1">
       <c r="A70" s="44" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B70" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-023-052</t>
+          <t>ACSMS-TC-023-051</t>
         </is>
       </c>
       <c r="C70" s="10" t="n"/>
       <c r="D70" s="11" t="n"/>
       <c r="E70" s="46" t="inlineStr">
         <is>
-          <t>Xử lý khi mất kết nối mạng</t>
+          <t>Link download trong email thông báo</t>
         </is>
       </c>
       <c r="F70" s="10" t="n"/>
@@ -15917,8 +15977,10 @@
       <c r="I70" s="11" t="n"/>
       <c r="J70" s="46" t="inlineStr">
         <is>
-          <t>・role: NICHINO_ADMIN
-・Đã đăng nhập + đã xác thực MFA</t>
+          <t>・Đăng nhập bằng role NICHINO_STAFF (có quyền `file.upload`)
+・「JA北海道」(ja_id=100) có từ 1 tài khoản trở lên với địa chỉ email nhận được thư
+・`FRONTEND_URL` đã được thiết lập (ví dụ: `https://acsms.example.com`)
+・Worker thông báo (file-upload-notification) đang chạy</t>
         </is>
       </c>
       <c r="K70" s="10" t="n"/>
@@ -15943,7 +16005,75 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Click「アップロード実行」ở trạng thái giả lập mất kết nối mạng ở tab Network của DevTools</t>
+            <t xml:space="preserve">Upload `増減通知 2026年04月.pdf` cho「JA北海道」và chờ đến khi trạng thái thông báo chuyển thành「完了」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra nội dung email thông báo đã nhận
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Mở link trong nội dung email bằng trình duyệt ở trạng thái chưa đăng nhập
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Đăng nhập bằng tài khoản JA_HONTEN của「JA北海道」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Thực hiện cùng các bước trên ở môi trường chưa thiết lập `FRONTEND_URL` và kiểm tra nội dung email</t>
           </r>
         </is>
       </c>
@@ -15969,15 +16099,108 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Toast lỗi mạng được hiển thị ở phía frontend
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Không phát sinh lỗi ngoài dự kiến (màn hình không bị terminate bất thường)</t>
+            <t xml:space="preserve">`notification_status` chuyển thành 3:完了
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nội dung có câu hướng dẫn「下記のリンクからダウンロードしてください。」và URL dạng `https://acsms.example.com/file-download?file_name=%E5%A2%97%E6%B8%9B%E9%80%9A%E7%9F%A5%202026%E5%B9%B404%E6%9C%88.pdf`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chuyển sang màn hình đăng nhập, URL có kèm tham số `redirect` (không hiển thị JSON 401)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chuyển sang màn hình download file, ô tìm kiếm tên file đã điền sẵn `増減通知 2026年04月.pdf` và chỉ file tương ứng hiển thị trong danh sách. Bấm tiếp「検索クリア」thì bộ lọc được gỡ bỏ
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Dòng link (câu hướng dẫn và URL) bị lược bỏ khỏi nội dung, các mục khác (tên JA・tên file・thời gian upload・người upload・footer chỉ gửi đi) vẫn xuất ra như cũ
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Tại thời điểm 2026-07 chủ trương là「không đưa URL tuyệt đối phụ thuộc môi trường vào nội dung email」, nhưng 2026-08 đã đổi thành「có đưa link」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Lý do không dùng link trực tiếp tới API (`/api/v1/file-download/{id}/download`): nếu chưa đăng nhập thì chỉ trả về JSON 401 và không có đường dẫn tới trang đăng nhập. Nếu là URL màn hình thì router guard sẽ đưa về đăng nhập rồi quay lại URL ban đầu sau khi xác thực
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Lý do bỏ hẳn dòng link khi `FRONTEND_URL` chưa thiết lập: để không đưa link hỏng kiểu `undefined/file-download` vào nội dung email</t>
           </r>
         </is>
       </c>
@@ -15989,7 +16212,7 @@
       <c r="AD70" s="11" t="n"/>
       <c r="AE70" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF70" s="11" t="n"/>
@@ -16023,7 +16246,12 @@
       <c r="BH70" s="45" t="inlineStr"/>
       <c r="BI70" s="10" t="n"/>
       <c r="BJ70" s="11" t="n"/>
-      <c r="BK70" s="46" t="inlineStr"/>
+      <c r="BK70" s="46" t="inlineStr">
+        <is>
+          <t>(không có)
+---</t>
+        </is>
+      </c>
       <c r="BL70" s="10" t="n"/>
       <c r="BM70" s="10" t="n"/>
       <c r="BN70" s="10" t="n"/>
@@ -16031,21 +16259,1023 @@
       <c r="BP70" s="10" t="n"/>
       <c r="BQ70" s="11" t="n"/>
     </row>
+    <row r="71" ht="450" customHeight="1">
+      <c r="A71" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-052</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>Preview từ danh sách (ảnh / PDF)</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN (có quyền `file.download`)
+・Tồn tại 1 file PDF・1 file ảnh・1 file Excel đã upload
+・Chuẩn bị thêm 1 file của JA khác và 1 file đã xóa logic</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="11" t="n"/>
+      <c r="Q71" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thực hiện thao tác preview file PDF ở danh sách file đã upload và kiểm tra response của GET `/api/v1/file-upload/{file_upload_id}/preview`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thực hiện thao tác tương tự với file ảnh
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chỉ định trực tiếp ID file ngoài phạm vi DataScope (JA khác) và gọi API preview
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chỉ định trực tiếp ID file đã xóa logic và gọi API preview
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Gọi API preview bằng role không có quyền `file.download`</t>
+          </r>
+        </is>
+      </c>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="11" t="n"/>
+      <c r="X71" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP status code 200 kèm `data.preview_url` (URL có chữ ký) và `data.file_name`. Mở URL hiển thị được file
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Preview được tương tự
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP status code 404 (`NOT_FOUND`) (che giấu sự tồn tại nên dùng 404 chứ không phải 403)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP status code 404 (`NOT_FOUND`) (bị loại theo điều kiện `deleted_at IS NULL`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP status code 403 (`FORBIDDEN`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Chức năng này đã từng bị xóa khỏi màn hình này vào 2026/07/02 và chuyển sang màn hình download (SCR-022), nhưng theo yêu cầu khách hàng đã được **thêm lại** trong cùng tháng (2026/07/27). Xem tài liệu thiết kế màn hình v1.4 / tài liệu thiết kế API v1.2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Preview chỉ phát hành URL có chữ ký, không INSERT vào `t_file_upload`</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="11" t="n"/>
+      <c r="AE71" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF71" s="11" t="n"/>
+      <c r="AG71" s="45" t="inlineStr"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="11" t="n"/>
+      <c r="AJ71" s="45" t="inlineStr"/>
+      <c r="AK71" s="10" t="n"/>
+      <c r="AL71" s="11" t="n"/>
+      <c r="AM71" s="45" t="inlineStr"/>
+      <c r="AN71" s="10" t="n"/>
+      <c r="AO71" s="11" t="n"/>
+      <c r="AP71" s="45" t="inlineStr"/>
+      <c r="AQ71" s="10" t="n"/>
+      <c r="AR71" s="11" t="n"/>
+      <c r="AS71" s="45" t="inlineStr"/>
+      <c r="AT71" s="10" t="n"/>
+      <c r="AU71" s="11" t="n"/>
+      <c r="AV71" s="45" t="inlineStr"/>
+      <c r="AW71" s="10" t="n"/>
+      <c r="AX71" s="11" t="n"/>
+      <c r="AY71" s="45" t="inlineStr"/>
+      <c r="AZ71" s="10" t="n"/>
+      <c r="BA71" s="11" t="n"/>
+      <c r="BB71" s="45" t="inlineStr"/>
+      <c r="BC71" s="10" t="n"/>
+      <c r="BD71" s="11" t="n"/>
+      <c r="BE71" s="45" t="inlineStr"/>
+      <c r="BF71" s="10" t="n"/>
+      <c r="BG71" s="11" t="n"/>
+      <c r="BH71" s="45" t="inlineStr"/>
+      <c r="BI71" s="10" t="n"/>
+      <c r="BJ71" s="11" t="n"/>
+      <c r="BK71" s="46" t="inlineStr">
+        <is>
+          <t>(không có)
+---</t>
+        </is>
+      </c>
+      <c r="BL71" s="10" t="n"/>
+      <c r="BM71" s="10" t="n"/>
+      <c r="BN71" s="10" t="n"/>
+      <c r="BO71" s="10" t="n"/>
+      <c r="BP71" s="10" t="n"/>
+      <c r="BQ71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="450" customHeight="1">
+      <c r="A72" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="B72" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-053</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="46" t="inlineStr">
+        <is>
+          <t>Download đơn lẻ từ danh sách và dấu vết</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN (có quyền `file.download`)
+・Tồn tại từ 1 file đã upload trở lên</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="11" t="n"/>
+      <c r="Q72" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ0 (đo trước)：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thực thi `SELECT COUNT(*) FROM t_file_download` trên DB và ghi lại tổng số trước khi test
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chọn 1 checkbox ở danh sách rồi thực hiện download, kiểm tra response của GET `/api/v1/file-upload/{file_upload_id}/download`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra nội dung file đã tải và `Content-Type`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thực thi lại `SELECT COUNT(*) FROM t_file_download` trên DB và so sánh với ステップ0
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thực thi `SELECT operation, log_type FROM t_log WHERE target_table = 't_file_upload' ORDER BY log_id DESC LIMIT 1` trên DB
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Chỉ định trực tiếp ID file ngoài phạm vi DataScope・đã xóa logic rồi gọi API download</t>
+          </r>
+        </is>
+      </c>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="11" t="n"/>
+      <c r="X72" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP status code 200, trả binary với `Content-Disposition: attachment; filename="..."`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nội dung khớp với file gốc. `Content-Type` được phán định đúng từ phần mở rộng (PDF → `application/pdf` v.v.)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Tổng số của `t_file_download` **không tăng**. Việc download ở màn hình này không INSERT vào `t_file_download` (quy cách cũ tạo dòng lịch sử với `download_type = 2`, cài đặt hiện tại thì không tạo)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Log thao tác `operation = 'DOWNLOAD'`・`log_type = 4` (FILE_OPERATION) được ghi lại
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Cả hai đều trả về HTTP status code 404 (`NOT_FOUND`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ステップ3 là kiểm tra hồi quy cho khác biệt với quy cách cũ. Đây là việc khác với xử lý đăng ký dòng cặp vào `t_file_download` lúc upload (#55935); thao tác download thì không làm tăng số dòng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Việc lấy file từ storage được thực hiện trước và nằm ngoài transaction, để khi lấy thất bại thì không để lại log thao tác</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="11" t="n"/>
+      <c r="AE72" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF72" s="11" t="n"/>
+      <c r="AG72" s="45" t="inlineStr"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="11" t="n"/>
+      <c r="AJ72" s="45" t="inlineStr"/>
+      <c r="AK72" s="10" t="n"/>
+      <c r="AL72" s="11" t="n"/>
+      <c r="AM72" s="45" t="inlineStr"/>
+      <c r="AN72" s="10" t="n"/>
+      <c r="AO72" s="11" t="n"/>
+      <c r="AP72" s="45" t="inlineStr"/>
+      <c r="AQ72" s="10" t="n"/>
+      <c r="AR72" s="11" t="n"/>
+      <c r="AS72" s="45" t="inlineStr"/>
+      <c r="AT72" s="10" t="n"/>
+      <c r="AU72" s="11" t="n"/>
+      <c r="AV72" s="45" t="inlineStr"/>
+      <c r="AW72" s="10" t="n"/>
+      <c r="AX72" s="11" t="n"/>
+      <c r="AY72" s="45" t="inlineStr"/>
+      <c r="AZ72" s="10" t="n"/>
+      <c r="BA72" s="11" t="n"/>
+      <c r="BB72" s="45" t="inlineStr"/>
+      <c r="BC72" s="10" t="n"/>
+      <c r="BD72" s="11" t="n"/>
+      <c r="BE72" s="45" t="inlineStr"/>
+      <c r="BF72" s="10" t="n"/>
+      <c r="BG72" s="11" t="n"/>
+      <c r="BH72" s="45" t="inlineStr"/>
+      <c r="BI72" s="10" t="n"/>
+      <c r="BJ72" s="11" t="n"/>
+      <c r="BK72" s="46" t="inlineStr">
+        <is>
+          <t>(không có)
+---</t>
+        </is>
+      </c>
+      <c r="BL72" s="10" t="n"/>
+      <c r="BM72" s="10" t="n"/>
+      <c r="BN72" s="10" t="n"/>
+      <c r="BO72" s="10" t="n"/>
+      <c r="BP72" s="10" t="n"/>
+      <c r="BQ72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="450" customHeight="1">
+      <c r="A73" s="44" t="n">
+        <v>54</v>
+      </c>
+      <c r="B73" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-023-054</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="46" t="inlineStr">
+        <is>
+          <t>Download hàng loạt ZIP từ danh sách (1〜50 file・không trùng)</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN (có quyền `file.download`)
+・Tồn tại từ 51 file đã upload trở lên
+・Chuẩn bị thêm 1 file ngoài phạm vi DataScope</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="11" t="n"/>
+      <c r="Q73" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chọn 3 file ở danh sách rồi thực hiện download ZIP hàng loạt, kiểm tra response của POST `/api/v1/file-upload/download-zip` và nội dung ZIP
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Gửi trực tiếp với `file_upload_ids: []` (0 phần tử)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Gửi trực tiếp với `file_upload_ids` gồm 51 ID duy nhất
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Gửi trực tiếp với `file_upload_ids` gồm 50 ID duy nhất (giá trị biên・đúng bằng giới hạn)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Gửi trực tiếp với `file_upload_ids: [id1, id1, id2]` (có trùng lặp)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Gửi trực tiếp với `file_upload_ids` có trộn đúng 1 ID ngoài phạm vi DataScope
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra số bản ghi được ghi vào `t_log`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ8：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Thực hiện download ZIP hàng loạt 21 lần trong 1 phút</t>
+          </r>
+        </is>
+      </c>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="11" t="n"/>
+      <c r="X73" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP status code 200・`Content-Type: application/zip`, ZIP chứa đủ cả 3 file đã chọn
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTP status code 400 (`VALIDATION_ERROR`, `errors[].message` là `ファイルを選択してください。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTP status code 400 (`errors[].message` là `一括ダウンロードは最大50件までです。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP status code 200 (50 nằm trong phạm vi cho phép)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTP status code 400 (`errors[].message` là `ファイルIDが重複しています。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP status code 404 (`NOT_FOUND`) và ZIP không được sinh ra. **Không có thành công một phần** (chỉ cần 1 file ngoài phạm vi là từ chối toàn bộ)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Log thao tác chỉ được ghi **1 bản ghi** cho cả ZIP (không ghi theo từng file)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ8：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Lần thứ 21 trả về HTTP status code 429 (`TOO_MANY_REQUESTS`) (giới hạn tốc độ 20 lần/phút)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Nếu chỉ định giá trị không phải số nguyên thì `ファイルIDは整数で指定してください。`, nếu không phải mảng thì `ファイルIDの形式が不正です。`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・「Không thành công một phần」ở ステップ6 là thiết kế từ chối toàn bộ, vì nếu thiếu file thì chỉ khi mở ZIP mới phát hiện ra</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="11" t="n"/>
+      <c r="AE73" s="45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF73" s="11" t="n"/>
+      <c r="AG73" s="45" t="inlineStr"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="11" t="n"/>
+      <c r="AJ73" s="45" t="inlineStr"/>
+      <c r="AK73" s="10" t="n"/>
+      <c r="AL73" s="11" t="n"/>
+      <c r="AM73" s="45" t="inlineStr"/>
+      <c r="AN73" s="10" t="n"/>
+      <c r="AO73" s="11" t="n"/>
+      <c r="AP73" s="45" t="inlineStr"/>
+      <c r="AQ73" s="10" t="n"/>
+      <c r="AR73" s="11" t="n"/>
+      <c r="AS73" s="45" t="inlineStr"/>
+      <c r="AT73" s="10" t="n"/>
+      <c r="AU73" s="11" t="n"/>
+      <c r="AV73" s="45" t="inlineStr"/>
+      <c r="AW73" s="10" t="n"/>
+      <c r="AX73" s="11" t="n"/>
+      <c r="AY73" s="45" t="inlineStr"/>
+      <c r="AZ73" s="10" t="n"/>
+      <c r="BA73" s="11" t="n"/>
+      <c r="BB73" s="45" t="inlineStr"/>
+      <c r="BC73" s="10" t="n"/>
+      <c r="BD73" s="11" t="n"/>
+      <c r="BE73" s="45" t="inlineStr"/>
+      <c r="BF73" s="10" t="n"/>
+      <c r="BG73" s="11" t="n"/>
+      <c r="BH73" s="45" t="inlineStr"/>
+      <c r="BI73" s="10" t="n"/>
+      <c r="BJ73" s="11" t="n"/>
+      <c r="BK73" s="46" t="inlineStr">
+        <is>
+          <t>(không có)
+---</t>
+        </is>
+      </c>
+      <c r="BL73" s="10" t="n"/>
+      <c r="BM73" s="10" t="n"/>
+      <c r="BN73" s="10" t="n"/>
+      <c r="BO73" s="10" t="n"/>
+      <c r="BP73" s="10" t="n"/>
+      <c r="BQ73" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="957">
+  <mergeCells count="992">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="Q27:W27"/>
+    <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="BK58:BQ58"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="AE54:AF54"/>
+    <mergeCell ref="BH33:BJ33"/>
     <mergeCell ref="BK50:BQ50"/>
     <mergeCell ref="AE41:AF41"/>
     <mergeCell ref="E52:I52"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="A45:BQ45"/>
     <mergeCell ref="AV57:AX57"/>
-    <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
     <mergeCell ref="AS61:AU61"/>
@@ -16054,14 +17284,14 @@
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
+    <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="AP45:AR45"/>
     <mergeCell ref="J64:P64"/>
-    <mergeCell ref="A46:BQ46"/>
     <mergeCell ref="BE13:BG13"/>
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
+    <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AM21:AO21"/>
     <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
@@ -16078,9 +17308,9 @@
     <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
     <mergeCell ref="AJ51:AL51"/>
+    <mergeCell ref="AP71:AR71"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
-    <mergeCell ref="X68:AD68"/>
     <mergeCell ref="Q40:W40"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
@@ -16088,9 +17318,11 @@
     <mergeCell ref="AV39:AX39"/>
     <mergeCell ref="AV70:AX70"/>
     <mergeCell ref="E58:I58"/>
+    <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
+    <mergeCell ref="AP73:AR73"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
@@ -16099,45 +17331,48 @@
     <mergeCell ref="X69:AD69"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
+    <mergeCell ref="B73:D73"/>
     <mergeCell ref="BB26:BD26"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
-    <mergeCell ref="AG45:AI45"/>
     <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="AJ33:AL33"/>
+    <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="J39:P39"/>
-    <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
-    <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
-    <mergeCell ref="BB27:BD27"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="AJ35:AL35"/>
     <mergeCell ref="BK37:BQ37"/>
-    <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
     <mergeCell ref="AE64:AF64"/>
     <mergeCell ref="AS62:AU62"/>
+    <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
+    <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
     <mergeCell ref="BK66:BQ66"/>
+    <mergeCell ref="A32:BQ32"/>
     <mergeCell ref="BK53:BQ53"/>
-    <mergeCell ref="BH60:BJ60"/>
+    <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
-    <mergeCell ref="AS64:AU64"/>
-    <mergeCell ref="AP68:AR68"/>
+    <mergeCell ref="Q72:W72"/>
     <mergeCell ref="J65:P65"/>
+    <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
+    <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="AP67:AR67"/>
@@ -16148,15 +17383,15 @@
     <mergeCell ref="BE41:BG41"/>
     <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
-    <mergeCell ref="BH55:BJ55"/>
+    <mergeCell ref="Q46:W46"/>
     <mergeCell ref="AM24:AO24"/>
-    <mergeCell ref="AG27:AI27"/>
+    <mergeCell ref="AJ72:AL72"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
     <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
+    <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
     <mergeCell ref="AV13:AX13"/>
     <mergeCell ref="BH42:BJ42"/>
@@ -16169,7 +17404,7 @@
     <mergeCell ref="AY44:BA44"/>
     <mergeCell ref="AV53:AX53"/>
     <mergeCell ref="BH44:BJ44"/>
-    <mergeCell ref="AS19:AU19"/>
+    <mergeCell ref="Q56:W56"/>
     <mergeCell ref="AE52:AF52"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
@@ -16182,13 +17417,14 @@
     <mergeCell ref="BH24:BJ24"/>
     <mergeCell ref="J13:P13"/>
     <mergeCell ref="BE34:BG34"/>
+    <mergeCell ref="BE28:BG28"/>
     <mergeCell ref="AJ41:AL41"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
     <mergeCell ref="J53:P53"/>
     <mergeCell ref="AS14:AU14"/>
     <mergeCell ref="AE53:AF53"/>
-    <mergeCell ref="AG55:AI55"/>
+    <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="AP18:AR18"/>
     <mergeCell ref="BH26:BJ26"/>
     <mergeCell ref="AG38:AI38"/>
@@ -16197,15 +17433,16 @@
     <mergeCell ref="AY70:BA70"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
-    <mergeCell ref="J55:P55"/>
     <mergeCell ref="BE29:BG29"/>
-    <mergeCell ref="AY32:BA32"/>
+    <mergeCell ref="BK28:BQ28"/>
+    <mergeCell ref="BB33:BD33"/>
+    <mergeCell ref="AG46:AI46"/>
     <mergeCell ref="Q34:W34"/>
     <mergeCell ref="AG40:AI40"/>
     <mergeCell ref="X24:AD24"/>
     <mergeCell ref="BB43:BD43"/>
-    <mergeCell ref="BK68:BQ68"/>
     <mergeCell ref="AY47:BA47"/>
+    <mergeCell ref="AS72:AU72"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
@@ -16213,6 +17450,7 @@
     <mergeCell ref="AJ67:AL67"/>
     <mergeCell ref="Q30:W30"/>
     <mergeCell ref="BK67:BQ67"/>
+    <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
@@ -16220,57 +17458,57 @@
     <mergeCell ref="AP44:AR44"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="AJ69:AL69"/>
     <mergeCell ref="BK69:BQ69"/>
     <mergeCell ref="AM70:AO70"/>
+    <mergeCell ref="AE71:AF71"/>
     <mergeCell ref="BE43:BG43"/>
+    <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
-    <mergeCell ref="AV68:AX68"/>
     <mergeCell ref="BB59:BD59"/>
-    <mergeCell ref="X27:AD27"/>
+    <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="AG66:AI66"/>
+    <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="AY60:BA60"/>
     <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
-    <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
-    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="AP72:AR72"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
-    <mergeCell ref="J68:P68"/>
     <mergeCell ref="AY18:BA18"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="AY45:BA45"/>
+    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="E36:I36"/>
-    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="BH70:BJ70"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AV65:AX65"/>
-    <mergeCell ref="BH45:BJ45"/>
+    <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
-    <mergeCell ref="BH32:BJ32"/>
     <mergeCell ref="BK18:BQ18"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A19:BQ19"/>
     <mergeCell ref="AY22:BA22"/>
+    <mergeCell ref="A68:BQ68"/>
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="AS22:AU22"/>
+    <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="BH72:BJ72"/>
     <mergeCell ref="AP26:AR26"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AY42:BA42"/>
-    <mergeCell ref="AE55:AF55"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="X38:AD38"/>
     <mergeCell ref="B42:D42"/>
+    <mergeCell ref="BH46:BJ46"/>
     <mergeCell ref="BE50:BG50"/>
     <mergeCell ref="BE44:BG44"/>
-    <mergeCell ref="AP19:AR19"/>
     <mergeCell ref="AJ57:AL57"/>
     <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
@@ -16285,18 +17523,23 @@
     <mergeCell ref="AV34:AX34"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="BH58:BJ58"/>
+    <mergeCell ref="AV28:AX28"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
     <mergeCell ref="AG62:AI62"/>
+    <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="X40:AD40"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="AV36:AX36"/>
     <mergeCell ref="T6:V6"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="AV30:AX30"/>
+    <mergeCell ref="AE73:AF73"/>
     <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="AS33:AU33"/>
     <mergeCell ref="AM36:AO36"/>
     <mergeCell ref="F1:Q1"/>
     <mergeCell ref="AP37:AR37"/>
@@ -16304,20 +17547,18 @@
     <mergeCell ref="E26:I26"/>
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="BE65:BG65"/>
+    <mergeCell ref="BK72:BQ72"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
-    <mergeCell ref="AE68:AF68"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
-    <mergeCell ref="A63:BQ63"/>
     <mergeCell ref="AY66:BA66"/>
+    <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AV21:AX21"/>
-    <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
-    <mergeCell ref="X45:AD45"/>
     <mergeCell ref="E50:I50"/>
     <mergeCell ref="AG11:AI11"/>
     <mergeCell ref="BH53:BJ53"/>
@@ -16326,21 +17567,22 @@
     <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AP63:AR63"/>
+    <mergeCell ref="E42:I42"/>
     <mergeCell ref="Q65:W65"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="AY55:BA55"/>
-    <mergeCell ref="AY68:BA68"/>
+    <mergeCell ref="BH71:BJ71"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
-    <mergeCell ref="BK19:BQ19"/>
+    <mergeCell ref="X46:AD46"/>
     <mergeCell ref="AE21:AF21"/>
+    <mergeCell ref="BH73:BJ73"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
-    <mergeCell ref="AP27:AR27"/>
+    <mergeCell ref="AS28:AU28"/>
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="BE39:BG39"/>
     <mergeCell ref="J29:P29"/>
@@ -16353,24 +17595,21 @@
     <mergeCell ref="AV49:AX49"/>
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
-    <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
-    <mergeCell ref="AJ60:AL60"/>
-    <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
     <mergeCell ref="J24:P24"/>
     <mergeCell ref="AG51:AI51"/>
+    <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="E70:I70"/>
     <mergeCell ref="Q14:W14"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="AV50:AX50"/>
-    <mergeCell ref="Q60:W60"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="AS54:AU54"/>
-    <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
     <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
@@ -16378,16 +17617,16 @@
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="AG65:AI65"/>
-    <mergeCell ref="AV55:AX55"/>
+    <mergeCell ref="X73:AD73"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="AV52:AX52"/>
-    <mergeCell ref="AP55:AR55"/>
+    <mergeCell ref="AS56:AU56"/>
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
-    <mergeCell ref="BH68:BJ68"/>
+    <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
@@ -16401,11 +17640,13 @@
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="BH67:BJ67"/>
+    <mergeCell ref="BE71:BG71"/>
     <mergeCell ref="J42:P42"/>
+    <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AY67:BA67"/>
+    <mergeCell ref="BB72:BD72"/>
     <mergeCell ref="Q13:W13"/>
-    <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
@@ -16414,21 +17655,18 @@
     <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="BE66:BG66"/>
     <mergeCell ref="AY69:BA69"/>
-    <mergeCell ref="E60:I60"/>
+    <mergeCell ref="Q71:W71"/>
     <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
-    <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="X61:AD61"/>
-    <mergeCell ref="BK27:BQ27"/>
+    <mergeCell ref="Q33:W33"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AE29:AF29"/>
     <mergeCell ref="B41:D41"/>
-    <mergeCell ref="AV45:AX45"/>
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="AV32:AX32"/>
     <mergeCell ref="AV26:AX26"/>
-    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="Q73:W73"/>
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
     <mergeCell ref="X62:AD62"/>
@@ -16436,18 +17674,16 @@
     <mergeCell ref="B66:D66"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="BB19:BD19"/>
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
     <mergeCell ref="J70:P70"/>
-    <mergeCell ref="A28:BQ28"/>
     <mergeCell ref="AS44:AU44"/>
-    <mergeCell ref="AV27:AX27"/>
-    <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="AM71:AO71"/>
     <mergeCell ref="X64:AD64"/>
+    <mergeCell ref="AG72:AI72"/>
     <mergeCell ref="BH18:BJ18"/>
-    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="J63:P63"/>
     <mergeCell ref="AE26:AF26"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
@@ -16456,60 +17692,64 @@
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
+    <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
+    <mergeCell ref="AJ28:AL28"/>
+    <mergeCell ref="E71:I71"/>
     <mergeCell ref="BK17:BQ17"/>
-    <mergeCell ref="BK55:BQ55"/>
-    <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
+    <mergeCell ref="E73:I73"/>
+    <mergeCell ref="AP46:AR46"/>
     <mergeCell ref="BK59:BQ59"/>
+    <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
     <mergeCell ref="AE42:AF42"/>
     <mergeCell ref="AS57:AU57"/>
-    <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
     <mergeCell ref="Q21:W21"/>
     <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
     <mergeCell ref="B64:D64"/>
-    <mergeCell ref="A56:BQ56"/>
+    <mergeCell ref="A27:BQ27"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
-    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
+    <mergeCell ref="AP56:AR56"/>
+    <mergeCell ref="AG20:AI20"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM53:AO53"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
-    <mergeCell ref="J45:P45"/>
     <mergeCell ref="Q35:W35"/>
-    <mergeCell ref="AM19:AO19"/>
+    <mergeCell ref="BB71:BD71"/>
+    <mergeCell ref="AM46:AO46"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
     <mergeCell ref="E66:I66"/>
+    <mergeCell ref="AV71:AX71"/>
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AE70:AF70"/>
+    <mergeCell ref="AY72:BA72"/>
     <mergeCell ref="AM48:AO48"/>
+    <mergeCell ref="BB73:BD73"/>
     <mergeCell ref="Q49:W49"/>
-    <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AM44:AO44"/>
+    <mergeCell ref="AV73:AX73"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
-    <mergeCell ref="E55:I55"/>
-    <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
     <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
@@ -16526,12 +17766,12 @@
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="AS70:AU70"/>
+    <mergeCell ref="J71:P71"/>
+    <mergeCell ref="X72:AD72"/>
+    <mergeCell ref="AM73:AO73"/>
     <mergeCell ref="J58:P58"/>
-    <mergeCell ref="AS32:AU32"/>
-    <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
     <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="BH19:BJ19"/>
     <mergeCell ref="X70:AD70"/>
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="BE23:BG23"/>
@@ -16539,40 +17779,40 @@
     <mergeCell ref="BK30:BQ30"/>
     <mergeCell ref="BK36:BQ36"/>
     <mergeCell ref="AS47:AU47"/>
+    <mergeCell ref="J73:P73"/>
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AJ29:AL29"/>
+    <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
     <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="BE18:BG18"/>
-    <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="Q29:W29"/>
     <mergeCell ref="AG35:AI35"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
-    <mergeCell ref="B62:D62"/>
     <mergeCell ref="AV66:AX66"/>
-    <mergeCell ref="X19:AD19"/>
-    <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="B72:D72"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
     <mergeCell ref="AP62:AR62"/>
     <mergeCell ref="E16:I16"/>
+    <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
     <mergeCell ref="BE49:BG49"/>
     <mergeCell ref="AS50:AU50"/>
     <mergeCell ref="E10:I11"/>
+    <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="B70:D70"/>
-    <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
-    <mergeCell ref="AS60:AU60"/>
     <mergeCell ref="AV61:AX61"/>
     <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="Z7:AB7"/>
@@ -16584,20 +17824,21 @@
     <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="AM67:AO67"/>
-    <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
     <mergeCell ref="AE59:AF59"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
+    <mergeCell ref="J46:P46"/>
+    <mergeCell ref="AE46:AF46"/>
     <mergeCell ref="BB35:BD35"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
     <mergeCell ref="AP65:AR65"/>
+    <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AM69:AO69"/>
     <mergeCell ref="AJ24:AL24"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
@@ -16617,23 +17858,26 @@
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
-    <mergeCell ref="BH27:BJ27"/>
-    <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
+    <mergeCell ref="BH20:BJ20"/>
     <mergeCell ref="AG54:AI54"/>
-    <mergeCell ref="BH69:BJ69"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="BH25:BJ25"/>
     <mergeCell ref="AM38:AO38"/>
+    <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
+    <mergeCell ref="BH69:BJ69"/>
+    <mergeCell ref="AS73:AU73"/>
+    <mergeCell ref="E72:I72"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
     <mergeCell ref="AJ52:AL52"/>
     <mergeCell ref="BH22:BJ22"/>
     <mergeCell ref="BK52:BQ52"/>
+    <mergeCell ref="AG56:AI56"/>
     <mergeCell ref="BE26:BG26"/>
     <mergeCell ref="J16:P16"/>
     <mergeCell ref="AJ39:AL39"/>
@@ -16655,11 +17899,9 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="Q70:W70"/>
     <mergeCell ref="AE66:AF66"/>
-    <mergeCell ref="Q45:W45"/>
     <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
-    <mergeCell ref="Q32:W32"/>
     <mergeCell ref="AY35:BA35"/>
     <mergeCell ref="X22:AD22"/>
     <mergeCell ref="BH38:BJ38"/>
@@ -16667,51 +17909,52 @@
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
     <mergeCell ref="AS66:AU66"/>
-    <mergeCell ref="E19:I19"/>
     <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BK65:BQ65"/>
     <mergeCell ref="J67:P67"/>
     <mergeCell ref="BK21:BQ21"/>
+    <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
     <mergeCell ref="AE67:AF67"/>
     <mergeCell ref="AV64:AX64"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
-    <mergeCell ref="AS68:AU68"/>
-    <mergeCell ref="AJ32:AL32"/>
+    <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="J69:P69"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="Q58:W58"/>
     <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
+    <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
-    <mergeCell ref="A20:BQ20"/>
-    <mergeCell ref="AJ27:AL27"/>
+    <mergeCell ref="AM72:AO72"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="AY41:BA41"/>
     <mergeCell ref="X15:AD15"/>
     <mergeCell ref="AV18:AX18"/>
     <mergeCell ref="E37:I37"/>
+    <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
+    <mergeCell ref="AY56:BA56"/>
     <mergeCell ref="AM59:AO59"/>
     <mergeCell ref="AV11:AX11"/>
+    <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AS21:AU21"/>
     <mergeCell ref="AY43:BA43"/>
-    <mergeCell ref="BE32:BG32"/>
+    <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
     <mergeCell ref="AE16:AF16"/>
-    <mergeCell ref="AG32:AI32"/>
     <mergeCell ref="X35:AD35"/>
     <mergeCell ref="AE10:AF11"/>
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
-    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
@@ -16721,101 +17964,108 @@
     <mergeCell ref="BB44:BD44"/>
     <mergeCell ref="AJ53:AL53"/>
     <mergeCell ref="AV10:BJ10"/>
-    <mergeCell ref="BE27:BG27"/>
+    <mergeCell ref="BH28:BJ28"/>
     <mergeCell ref="J17:P17"/>
     <mergeCell ref="AM54:AO54"/>
     <mergeCell ref="AV44:AX44"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="AG57:AI57"/>
+    <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="BB52:BD52"/>
-    <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
-    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="BB70:BD70"/>
     <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
-    <mergeCell ref="BB45:BD45"/>
     <mergeCell ref="AG58:AI58"/>
-    <mergeCell ref="BB32:BD32"/>
-    <mergeCell ref="Q55:W55"/>
-    <mergeCell ref="A33:BQ33"/>
     <mergeCell ref="AY36:BA36"/>
-    <mergeCell ref="E27:I27"/>
     <mergeCell ref="AS49:AU49"/>
     <mergeCell ref="X34:AD34"/>
+    <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
+    <mergeCell ref="BB47:BD47"/>
     <mergeCell ref="AE69:AF69"/>
-    <mergeCell ref="BB47:BD47"/>
-    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
+    <mergeCell ref="AJ71:AL71"/>
+    <mergeCell ref="AP33:AR33"/>
+    <mergeCell ref="BK71:BQ71"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
-    <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
     <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="AS69:AU69"/>
+    <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
+    <mergeCell ref="AJ73:AL73"/>
     <mergeCell ref="AP35:AR35"/>
+    <mergeCell ref="BK73:BQ73"/>
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
     <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="AY62:BA62"/>
+    <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="AJ66:AL66"/>
+    <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="AG70:AI70"/>
+    <mergeCell ref="AE72:AF72"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
+    <mergeCell ref="BK20:BQ20"/>
+    <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
-    <mergeCell ref="AJ68:AL68"/>
-    <mergeCell ref="AV19:AX19"/>
     <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="AY51:BA51"/>
     <mergeCell ref="Q53:W53"/>
+    <mergeCell ref="X56:AD56"/>
     <mergeCell ref="BK22:BQ22"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
+    <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="Q68:W68"/>
     <mergeCell ref="E40:I40"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="BE73:BG73"/>
     <mergeCell ref="E15:I15"/>
+    <mergeCell ref="AV20:AX20"/>
     <mergeCell ref="BE48:BG48"/>
     <mergeCell ref="AS24:AU24"/>
     <mergeCell ref="AS18:AU18"/>
-    <mergeCell ref="AM27:AO27"/>
     <mergeCell ref="BH36:BJ36"/>
     <mergeCell ref="BH11:BJ11"/>
-    <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="Z6:AB6"/>
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AE65:AF65"/>
+    <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
-    <mergeCell ref="J27:P27"/>
     <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AY33:BA33"/>
     <mergeCell ref="BB53:BD53"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AM22:AO22"/>
     <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="J20:P20"/>
     <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
-    <mergeCell ref="BB55:BD55"/>
+    <mergeCell ref="BK33:BQ33"/>
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="BH62:BJ62"/>
@@ -16833,24 +18083,28 @@
     <mergeCell ref="Q10:W11"/>
     <mergeCell ref="BB25:BD25"/>
     <mergeCell ref="AP49:AR49"/>
+    <mergeCell ref="E28:I28"/>
     <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="BE67:BG67"/>
+    <mergeCell ref="AV33:AX33"/>
     <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="J38:P38"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="Q28:W28"/>
     <mergeCell ref="E30:I30"/>
     <mergeCell ref="BE69:BG69"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
-    <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A55:BQ55"/>
     <mergeCell ref="E59:I59"/>
+    <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
@@ -16861,6 +18115,7 @@
     <mergeCell ref="E61:I61"/>
     <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="Q67:W67"/>
+    <mergeCell ref="AG73:AI73"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -16869,29 +18124,30 @@
     <mergeCell ref="BE64:BG64"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
-    <mergeCell ref="BB68:BD68"/>
+    <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
     <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AM66:AO66"/>
     <mergeCell ref="Q69:W69"/>
-    <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
+    <mergeCell ref="E56:I56"/>
     <mergeCell ref="AP29:AR29"/>
     <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
+    <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
-    <mergeCell ref="BK29:BQ29"/>
+    <mergeCell ref="AE20:AF20"/>
     <mergeCell ref="BK23:BQ23"/>
     <mergeCell ref="AE25:AF25"/>
+    <mergeCell ref="BK29:BQ29"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
-    <mergeCell ref="AM68:AO68"/>
     <mergeCell ref="BH52:BJ52"/>
-    <mergeCell ref="AS27:AU27"/>
+    <mergeCell ref="A60:BQ60"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="AE35:AF35"/>
     <mergeCell ref="BH14:BJ14"/>
@@ -16900,18 +18156,23 @@
     <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
+    <mergeCell ref="AY20:BA20"/>
+    <mergeCell ref="AG28:AI28"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
+    <mergeCell ref="J72:P72"/>
+    <mergeCell ref="J28:P28"/>
     <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
     <mergeCell ref="AG67:AI67"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
     <mergeCell ref="AV54:AX54"/>
@@ -16920,13 +18181,12 @@
     <mergeCell ref="J30:P30"/>
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
-    <mergeCell ref="AS45:AU45"/>
     <mergeCell ref="BK57:BQ57"/>
     <mergeCell ref="AG69:AI69"/>
     <mergeCell ref="AE40:AF40"/>
     <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
-    <mergeCell ref="Q19:W19"/>
+    <mergeCell ref="BH63:BJ63"/>
     <mergeCell ref="AS38:AU38"/>
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
@@ -16936,42 +18196,45 @@
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="AP52:AR52"/>
-    <mergeCell ref="X55:AD55"/>
+    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AM62:AO62"/>
+    <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
-    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="BE72:BG72"/>
+    <mergeCell ref="AY71:BA71"/>
     <mergeCell ref="E62:I62"/>
+    <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
+    <mergeCell ref="AS71:AU71"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AV72:AX72"/>
     <mergeCell ref="E64:I64"/>
+    <mergeCell ref="AY73:BA73"/>
+    <mergeCell ref="X71:AD71"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
-    <mergeCell ref="B55:D55"/>
     <mergeCell ref="AP70:AR70"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
-    <mergeCell ref="AP32:AR32"/>
-    <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BH64:BJ64"/>
     <mergeCell ref="X66:AD66"/>
-    <mergeCell ref="BE19:BG19"/>
-    <mergeCell ref="BK32:BQ32"/>
+    <mergeCell ref="AM33:AO33"/>
     <mergeCell ref="BK26:BQ26"/>
+    <mergeCell ref="AE28:AF28"/>
     <mergeCell ref="AP47:AR47"/>
     <mergeCell ref="BH30:BJ30"/>
     <mergeCell ref="AV31:AX31"/>
@@ -16981,24 +18244,26 @@
     <mergeCell ref="AE30:AF30"/>
     <mergeCell ref="Q26:W26"/>
     <mergeCell ref="AG10:AU10"/>
+    <mergeCell ref="B71:D71"/>
     <mergeCell ref="AG44:AI44"/>
     <mergeCell ref="AV62:AX62"/>
+    <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="BE14:BG14"/>
     <mergeCell ref="BB24:BD24"/>
-    <mergeCell ref="B58:D58"/>
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
-    <mergeCell ref="BE60:BG60"/>
+    <mergeCell ref="AV56:AX56"/>
+    <mergeCell ref="B58:D58"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE19 AE21:AE27 AE29:AE32 AE34:AE45 AE47:AE55 AE57:AE62 AE64:AE70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE31 AE33:AE44 AE46:AE54 AE56:AE59 AE61:AE67 AE69:AE73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG19 AG21:AG27 AG29:AG32 AG34:AG45 AG47:AG55 AG57:AG62 AG64:AG70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG31 AG33:AG44 AG46:AG54 AG56:AG59 AG61:AG67 AG69:AG73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV19 AV21:AV27 AV29:AV32 AV34:AV45 AV47:AV55 AV57:AV62 AV64:AV70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV31 AV33:AV44 AV46:AV54 AV56:AV59 AV61:AV67 AV69:AV73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
